--- a/trendstrategy_results_equity2025新.xlsx
+++ b/trendstrategy_results_equity2025新.xlsx
@@ -42598,7 +42598,7 @@
         <v>466</v>
       </c>
       <c r="D2">
-        <v>410.08</v>
+        <v>400.61</v>
       </c>
       <c r="E2">
         <v>24926</v>
@@ -42639,7 +42639,7 @@
         <v>466</v>
       </c>
       <c r="D3">
-        <v>89.98</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="E3">
         <v>115096</v>
@@ -42680,7 +42680,7 @@
         <v>466</v>
       </c>
       <c r="D4">
-        <v>141.4</v>
+        <v>144.46</v>
       </c>
       <c r="E4">
         <v>69124</v>
@@ -42721,7 +42721,7 @@
         <v>467</v>
       </c>
       <c r="D5">
-        <v>133.05</v>
+        <v>134.16</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -42885,7 +42885,7 @@
         <v>466</v>
       </c>
       <c r="D9">
-        <v>37.6</v>
+        <v>37.84</v>
       </c>
       <c r="E9">
         <v>263894</v>
@@ -42967,7 +42967,7 @@
         <v>467</v>
       </c>
       <c r="D11">
-        <v>36.59</v>
+        <v>37.08</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -43008,7 +43008,7 @@
         <v>466</v>
       </c>
       <c r="D12">
-        <v>57.34</v>
+        <v>56.05</v>
       </c>
       <c r="E12">
         <v>178158</v>
@@ -43172,7 +43172,7 @@
         <v>467</v>
       </c>
       <c r="D16">
-        <v>403.49</v>
+        <v>415.02</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -43254,7 +43254,7 @@
         <v>466</v>
       </c>
       <c r="D18">
-        <v>88.19</v>
+        <v>87.83</v>
       </c>
       <c r="E18">
         <v>113694</v>
@@ -43295,7 +43295,7 @@
         <v>466</v>
       </c>
       <c r="D19">
-        <v>36.27</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>277382</v>
@@ -43336,7 +43336,7 @@
         <v>467</v>
       </c>
       <c r="D20">
-        <v>83.8</v>
+        <v>85.67</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -43377,7 +43377,7 @@
         <v>466</v>
       </c>
       <c r="D21">
-        <v>65.95</v>
+        <v>65.5</v>
       </c>
       <c r="E21">
         <v>152454</v>
@@ -43623,7 +43623,7 @@
         <v>467</v>
       </c>
       <c r="D27">
-        <v>60.77</v>
+        <v>62.95</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -43664,7 +43664,7 @@
         <v>466</v>
       </c>
       <c r="D28">
-        <v>231.79</v>
+        <v>230.47</v>
       </c>
       <c r="E28">
         <v>43327</v>
@@ -43746,7 +43746,7 @@
         <v>467</v>
       </c>
       <c r="D30">
-        <v>228.27</v>
+        <v>230.91</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -43787,7 +43787,7 @@
         <v>466</v>
       </c>
       <c r="D31">
-        <v>64.77</v>
+        <v>63.77</v>
       </c>
       <c r="E31">
         <v>156590</v>
@@ -43869,7 +43869,7 @@
         <v>467</v>
       </c>
       <c r="D33">
-        <v>63.22</v>
+        <v>60.04</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -43910,7 +43910,7 @@
         <v>466</v>
       </c>
       <c r="D34">
-        <v>599.8099999999999</v>
+        <v>601.62</v>
       </c>
       <c r="E34">
         <v>16598</v>
@@ -44566,7 +44566,7 @@
         <v>467</v>
       </c>
       <c r="D50">
-        <v>108</v>
+        <v>116.52</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -44648,7 +44648,7 @@
         <v>466</v>
       </c>
       <c r="D52">
-        <v>112.8</v>
+        <v>104.62</v>
       </c>
       <c r="E52">
         <v>95448</v>
@@ -44730,7 +44730,7 @@
         <v>467</v>
       </c>
       <c r="D54">
-        <v>93.7</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -44771,7 +44771,7 @@
         <v>467</v>
       </c>
       <c r="D55">
-        <v>875.25</v>
+        <v>878.87</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -44812,7 +44812,7 @@
         <v>466</v>
       </c>
       <c r="D56">
-        <v>113.38</v>
+        <v>116.07</v>
       </c>
       <c r="E56">
         <v>86032</v>
@@ -44853,7 +44853,7 @@
         <v>466</v>
       </c>
       <c r="D57">
-        <v>180.54</v>
+        <v>179.7</v>
       </c>
       <c r="E57">
         <v>55569</v>
@@ -45099,7 +45099,7 @@
         <v>467</v>
       </c>
       <c r="D63">
-        <v>195.84</v>
+        <v>203.45</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -45140,7 +45140,7 @@
         <v>466</v>
       </c>
       <c r="D64">
-        <v>208.2</v>
+        <v>198.69</v>
       </c>
       <c r="E64">
         <v>50258</v>
@@ -45181,7 +45181,7 @@
         <v>466</v>
       </c>
       <c r="D65">
-        <v>72.17</v>
+        <v>73.92</v>
       </c>
       <c r="E65">
         <v>135088</v>
@@ -45386,7 +45386,7 @@
         <v>467</v>
       </c>
       <c r="D70">
-        <v>82.45</v>
+        <v>82.34</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -45427,7 +45427,7 @@
         <v>467</v>
       </c>
       <c r="D71">
-        <v>221.98</v>
+        <v>218.66</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -45468,7 +45468,7 @@
         <v>466</v>
       </c>
       <c r="D72">
-        <v>241</v>
+        <v>238.9</v>
       </c>
       <c r="E72">
         <v>41798</v>
@@ -45509,7 +45509,7 @@
         <v>466</v>
       </c>
       <c r="D73">
-        <v>75.56999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="E73">
         <v>131825</v>
@@ -45591,7 +45591,7 @@
         <v>467</v>
       </c>
       <c r="D75">
-        <v>159.54</v>
+        <v>143.86</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -45632,7 +45632,7 @@
         <v>466</v>
       </c>
       <c r="D76">
-        <v>156.85</v>
+        <v>152.37</v>
       </c>
       <c r="E76">
         <v>65536</v>
@@ -45755,7 +45755,7 @@
         <v>467</v>
       </c>
       <c r="D79">
-        <v>163.13</v>
+        <v>164.92</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -45796,7 +45796,7 @@
         <v>467</v>
       </c>
       <c r="D80">
-        <v>219.16</v>
+        <v>206.15</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -45837,7 +45837,7 @@
         <v>466</v>
       </c>
       <c r="D81">
-        <v>193.04</v>
+        <v>196.36</v>
       </c>
       <c r="E81">
         <v>50854</v>
@@ -45878,7 +45878,7 @@
         <v>466</v>
       </c>
       <c r="D82">
-        <v>219.16</v>
+        <v>206.15</v>
       </c>
       <c r="E82">
         <v>48439</v>
@@ -45960,7 +45960,7 @@
         <v>467</v>
       </c>
       <c r="D84">
-        <v>73.56</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -46001,7 +46001,7 @@
         <v>467</v>
       </c>
       <c r="D85">
-        <v>194.7</v>
+        <v>192.22</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -46042,7 +46042,7 @@
         <v>466</v>
       </c>
       <c r="D86">
-        <v>59.27</v>
+        <v>59.2</v>
       </c>
       <c r="E86">
         <v>168678</v>
@@ -46083,7 +46083,7 @@
         <v>466</v>
       </c>
       <c r="D87">
-        <v>168.95</v>
+        <v>168.5</v>
       </c>
       <c r="E87">
         <v>59262</v>
@@ -46165,7 +46165,7 @@
         <v>467</v>
       </c>
       <c r="D89">
-        <v>146.54</v>
+        <v>154.16</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -46206,7 +46206,7 @@
         <v>467</v>
       </c>
       <c r="D90">
-        <v>53.81</v>
+        <v>55.14</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -46247,7 +46247,7 @@
         <v>467</v>
       </c>
       <c r="D91">
-        <v>222.1</v>
+        <v>235.96</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -46288,7 +46288,7 @@
         <v>466</v>
       </c>
       <c r="D92">
-        <v>569.52</v>
+        <v>585.37</v>
       </c>
       <c r="E92">
         <v>17058</v>
@@ -46329,7 +46329,7 @@
         <v>466</v>
       </c>
       <c r="D93">
-        <v>146.54</v>
+        <v>154.16</v>
       </c>
       <c r="E93">
         <v>64775</v>
@@ -46370,7 +46370,7 @@
         <v>466</v>
       </c>
       <c r="D94">
-        <v>53.81</v>
+        <v>55.14</v>
       </c>
       <c r="E94">
         <v>181098</v>
@@ -46411,7 +46411,7 @@
         <v>467</v>
       </c>
       <c r="D95">
-        <v>149.68</v>
+        <v>151.47</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -46452,7 +46452,7 @@
         <v>466</v>
       </c>
       <c r="D96">
-        <v>132.06</v>
+        <v>130.94</v>
       </c>
       <c r="E96">
         <v>76262</v>
@@ -46575,7 +46575,7 @@
         <v>467</v>
       </c>
       <c r="D99">
-        <v>57.87</v>
+        <v>55.61</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -46616,7 +46616,7 @@
         <v>467</v>
       </c>
       <c r="D100">
-        <v>631.23</v>
+        <v>612.88</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -46657,7 +46657,7 @@
         <v>466</v>
       </c>
       <c r="D101">
-        <v>100.85</v>
+        <v>98.95</v>
       </c>
       <c r="E101">
         <v>100917</v>
@@ -46698,7 +46698,7 @@
         <v>466</v>
       </c>
       <c r="D102">
-        <v>99.06999999999999</v>
+        <v>98.42</v>
       </c>
       <c r="E102">
         <v>101460</v>
@@ -46903,7 +46903,7 @@
         <v>467</v>
       </c>
       <c r="D107">
-        <v>96.45</v>
+        <v>89.67</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -46944,7 +46944,7 @@
         <v>466</v>
       </c>
       <c r="D108">
-        <v>109.52</v>
+        <v>110.5</v>
       </c>
       <c r="E108">
         <v>90368</v>
@@ -47067,7 +47067,7 @@
         <v>467</v>
       </c>
       <c r="D111">
-        <v>133.93</v>
+        <v>141.04</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -47108,7 +47108,7 @@
         <v>467</v>
       </c>
       <c r="D112">
-        <v>99.34999999999999</v>
+        <v>91.81</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -47149,7 +47149,7 @@
         <v>467</v>
       </c>
       <c r="D113">
-        <v>99.70999999999999</v>
+        <v>108.46</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -47190,7 +47190,7 @@
         <v>466</v>
       </c>
       <c r="D114">
-        <v>108.46</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="E114">
         <v>101906</v>
@@ -47231,7 +47231,7 @@
         <v>466</v>
       </c>
       <c r="D115">
-        <v>188.42</v>
+        <v>197.11</v>
       </c>
       <c r="E115">
         <v>50660</v>
@@ -47272,7 +47272,7 @@
         <v>466</v>
       </c>
       <c r="D116">
-        <v>91.81</v>
+        <v>93.78</v>
       </c>
       <c r="E116">
         <v>106480</v>
@@ -47313,7 +47313,7 @@
         <v>467</v>
       </c>
       <c r="D117">
-        <v>172.19</v>
+        <v>168.41</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -47354,7 +47354,7 @@
         <v>467</v>
       </c>
       <c r="D118">
-        <v>85.25</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -47395,7 +47395,7 @@
         <v>466</v>
       </c>
       <c r="D119">
-        <v>88.77</v>
+        <v>97.61</v>
       </c>
       <c r="E119">
         <v>102302</v>
@@ -47436,7 +47436,7 @@
         <v>466</v>
       </c>
       <c r="D120">
-        <v>905.15</v>
+        <v>926.2</v>
       </c>
       <c r="E120">
         <v>10781</v>
@@ -47518,7 +47518,7 @@
         <v>467</v>
       </c>
       <c r="D122">
-        <v>875.6799999999999</v>
+        <v>930.41</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -47559,7 +47559,7 @@
         <v>466</v>
       </c>
       <c r="D123">
-        <v>205.04</v>
+        <v>217.88</v>
       </c>
       <c r="E123">
         <v>45831</v>
@@ -47805,7 +47805,7 @@
         <v>467</v>
       </c>
       <c r="D129">
-        <v>104.08</v>
+        <v>103.89</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -47846,7 +47846,7 @@
         <v>466</v>
       </c>
       <c r="D130">
-        <v>170.98</v>
+        <v>163</v>
       </c>
       <c r="E130">
         <v>61262</v>
@@ -47969,7 +47969,7 @@
         <v>467</v>
       </c>
       <c r="D133">
-        <v>188.25</v>
+        <v>198</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -48010,7 +48010,7 @@
         <v>466</v>
       </c>
       <c r="D134">
-        <v>255.73</v>
+        <v>261.44</v>
       </c>
       <c r="E134">
         <v>38195</v>
@@ -48133,7 +48133,7 @@
         <v>467</v>
       </c>
       <c r="D137">
-        <v>257.64</v>
+        <v>259.06</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -48174,7 +48174,7 @@
         <v>466</v>
       </c>
       <c r="D138">
-        <v>964.09</v>
+        <v>1039.87</v>
       </c>
       <c r="E138">
         <v>9602</v>
@@ -48420,7 +48420,7 @@
         <v>467</v>
       </c>
       <c r="D144">
-        <v>168.21</v>
+        <v>178.04</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -48461,7 +48461,7 @@
         <v>467</v>
       </c>
       <c r="D145">
-        <v>1271.42</v>
+        <v>1263</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -48502,7 +48502,7 @@
         <v>466</v>
       </c>
       <c r="D146">
-        <v>182.31</v>
+        <v>178.37</v>
       </c>
       <c r="E146">
         <v>55983</v>
@@ -48543,7 +48543,7 @@
         <v>466</v>
       </c>
       <c r="D147">
-        <v>36.11</v>
+        <v>35.6</v>
       </c>
       <c r="E147">
         <v>280499</v>
@@ -48625,7 +48625,7 @@
         <v>467</v>
       </c>
       <c r="D149">
-        <v>35</v>
+        <v>35.09</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -48666,7 +48666,7 @@
         <v>467</v>
       </c>
       <c r="D150">
-        <v>287.73</v>
+        <v>292.64</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -48707,7 +48707,7 @@
         <v>466</v>
       </c>
       <c r="D151">
-        <v>368.22</v>
+        <v>366.33</v>
       </c>
       <c r="E151">
         <v>27258</v>
@@ -48748,7 +48748,7 @@
         <v>466</v>
       </c>
       <c r="D152">
-        <v>192.5</v>
+        <v>200.17</v>
       </c>
       <c r="E152">
         <v>49886</v>
@@ -48830,7 +48830,7 @@
         <v>467</v>
       </c>
       <c r="D154">
-        <v>177.72</v>
+        <v>175.09</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -48871,7 +48871,7 @@
         <v>466</v>
       </c>
       <c r="D155">
-        <v>30.1</v>
+        <v>27.86</v>
       </c>
       <c r="E155">
         <v>358426</v>
@@ -48994,7 +48994,7 @@
         <v>467</v>
       </c>
       <c r="D158">
-        <v>214.59</v>
+        <v>221.35</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -49035,7 +49035,7 @@
         <v>466</v>
       </c>
       <c r="D159">
-        <v>45.73</v>
+        <v>44.09</v>
       </c>
       <c r="E159">
         <v>226486</v>
@@ -49158,7 +49158,7 @@
         <v>467</v>
       </c>
       <c r="D162">
-        <v>30.35</v>
+        <v>31.23</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -49199,7 +49199,7 @@
         <v>467</v>
       </c>
       <c r="D163">
-        <v>42.39</v>
+        <v>45.73</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -49240,7 +49240,7 @@
         <v>467</v>
       </c>
       <c r="D164">
-        <v>465.54</v>
+        <v>483.24</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -49281,7 +49281,7 @@
         <v>466</v>
       </c>
       <c r="D165">
-        <v>475.34</v>
+        <v>484.85</v>
       </c>
       <c r="E165">
         <v>20595</v>
@@ -49322,7 +49322,7 @@
         <v>466</v>
       </c>
       <c r="D166">
-        <v>31.23</v>
+        <v>33.23</v>
       </c>
       <c r="E166">
         <v>300504</v>
@@ -49363,7 +49363,7 @@
         <v>466</v>
       </c>
       <c r="D167">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="E167">
         <v>7862811</v>
@@ -49404,7 +49404,7 @@
         <v>467</v>
       </c>
       <c r="D168">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -49445,7 +49445,7 @@
         <v>466</v>
       </c>
       <c r="D169">
-        <v>34.47</v>
+        <v>33.25</v>
       </c>
       <c r="E169">
         <v>300323</v>
@@ -49568,7 +49568,7 @@
         <v>467</v>
       </c>
       <c r="D172">
-        <v>496.26</v>
+        <v>527.63</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -49609,7 +49609,7 @@
         <v>467</v>
       </c>
       <c r="D173">
-        <v>30.07</v>
+        <v>28.9</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -49650,7 +49650,7 @@
         <v>466</v>
       </c>
       <c r="D174">
-        <v>486.11</v>
+        <v>445.92</v>
       </c>
       <c r="E174">
         <v>22393</v>
@@ -49691,7 +49691,7 @@
         <v>466</v>
       </c>
       <c r="D175">
-        <v>103.21</v>
+        <v>102.37</v>
       </c>
       <c r="E175">
         <v>97545</v>
@@ -49773,7 +49773,7 @@
         <v>467</v>
       </c>
       <c r="D177">
-        <v>38.31</v>
+        <v>38.72</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -49814,7 +49814,7 @@
         <v>467</v>
       </c>
       <c r="D178">
-        <v>502.38</v>
+        <v>524.38</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -49855,7 +49855,7 @@
         <v>466</v>
       </c>
       <c r="D179">
-        <v>37.68</v>
+        <v>34.39</v>
       </c>
       <c r="E179">
         <v>290368</v>
@@ -49896,7 +49896,7 @@
         <v>466</v>
       </c>
       <c r="D180">
-        <v>502.91</v>
+        <v>530.48</v>
       </c>
       <c r="E180">
         <v>18824</v>
@@ -49978,7 +49978,7 @@
         <v>467</v>
       </c>
       <c r="D182">
-        <v>119.49</v>
+        <v>131.05</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -50019,7 +50019,7 @@
         <v>466</v>
       </c>
       <c r="D183">
-        <v>127.63</v>
+        <v>124.2</v>
       </c>
       <c r="E183">
         <v>80400</v>
@@ -50142,7 +50142,7 @@
         <v>467</v>
       </c>
       <c r="D186">
-        <v>112.64</v>
+        <v>111.35</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -50183,7 +50183,7 @@
         <v>466</v>
       </c>
       <c r="D187">
-        <v>18.86</v>
+        <v>18.06</v>
       </c>
       <c r="E187">
         <v>552921</v>
@@ -50306,7 +50306,7 @@
         <v>467</v>
       </c>
       <c r="D190">
-        <v>579.92</v>
+        <v>604.64</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -50347,7 +50347,7 @@
         <v>467</v>
       </c>
       <c r="D191">
-        <v>34.13</v>
+        <v>35.49</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -50388,7 +50388,7 @@
         <v>467</v>
       </c>
       <c r="D192">
-        <v>17.65</v>
+        <v>16.44</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -50429,7 +50429,7 @@
         <v>466</v>
       </c>
       <c r="D193">
-        <v>611.29</v>
+        <v>568.72</v>
       </c>
       <c r="E193">
         <v>17558</v>
@@ -50470,7 +50470,7 @@
         <v>466</v>
       </c>
       <c r="D194">
-        <v>33.96</v>
+        <v>30.72</v>
       </c>
       <c r="E194">
         <v>325057</v>
@@ -50511,7 +50511,7 @@
         <v>466</v>
       </c>
       <c r="D195">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="E195">
         <v>8053040</v>
@@ -50552,7 +50552,7 @@
         <v>467</v>
       </c>
       <c r="D196">
-        <v>36.69</v>
+        <v>35.79</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -50593,7 +50593,7 @@
         <v>467</v>
       </c>
       <c r="D197">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -50634,7 +50634,7 @@
         <v>466</v>
       </c>
       <c r="D198">
-        <v>34.74</v>
+        <v>33.28</v>
       </c>
       <c r="E198">
         <v>300053</v>
@@ -50675,7 +50675,7 @@
         <v>466</v>
       </c>
       <c r="D199">
-        <v>58.12</v>
+        <v>58.46</v>
       </c>
       <c r="E199">
         <v>170813</v>
@@ -50757,7 +50757,7 @@
         <v>467</v>
       </c>
       <c r="D201">
-        <v>503.72</v>
+        <v>517.1</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -50798,7 +50798,7 @@
         <v>467</v>
       </c>
       <c r="D202">
-        <v>55.69</v>
+        <v>53.79</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -50839,7 +50839,7 @@
         <v>467</v>
       </c>
       <c r="D203">
-        <v>33.77</v>
+        <v>32.47</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -50880,7 +50880,7 @@
         <v>466</v>
       </c>
       <c r="D204">
-        <v>35.5</v>
+        <v>33.23</v>
       </c>
       <c r="E204">
         <v>300504</v>
@@ -50962,7 +50962,7 @@
         <v>466</v>
       </c>
       <c r="D206">
-        <v>59.83</v>
+        <v>58.16</v>
       </c>
       <c r="E206">
         <v>171694</v>
@@ -51003,7 +51003,7 @@
         <v>467</v>
       </c>
       <c r="D207">
-        <v>33.67</v>
+        <v>32.17</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -51044,7 +51044,7 @@
         <v>467</v>
       </c>
       <c r="D208">
-        <v>56.76</v>
+        <v>57.37</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -51085,7 +51085,7 @@
         <v>467</v>
       </c>
       <c r="D209">
-        <v>14.12</v>
+        <v>14.47</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -51126,7 +51126,7 @@
         <v>466</v>
       </c>
       <c r="D210">
-        <v>32.28</v>
+        <v>32.68</v>
       </c>
       <c r="E210">
         <v>305562</v>
@@ -51167,7 +51167,7 @@
         <v>466</v>
       </c>
       <c r="D211">
-        <v>58.12</v>
+        <v>57.42</v>
       </c>
       <c r="E211">
         <v>173907</v>
@@ -51208,7 +51208,7 @@
         <v>466</v>
       </c>
       <c r="D212">
-        <v>18.03</v>
+        <v>19.08</v>
       </c>
       <c r="E212">
         <v>523363</v>
@@ -51249,7 +51249,7 @@
         <v>467</v>
       </c>
       <c r="D213">
-        <v>30.93</v>
+        <v>31.18</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -51290,7 +51290,7 @@
         <v>466</v>
       </c>
       <c r="D214">
-        <v>60.36</v>
+        <v>63.58</v>
       </c>
       <c r="E214">
         <v>157058</v>
@@ -51413,7 +51413,7 @@
         <v>467</v>
       </c>
       <c r="D217">
-        <v>54.05</v>
+        <v>55.69</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -51454,7 +51454,7 @@
         <v>466</v>
       </c>
       <c r="D218">
-        <v>13.57</v>
+        <v>14.08</v>
       </c>
       <c r="E218">
         <v>709216</v>
@@ -51577,7 +51577,7 @@
         <v>467</v>
       </c>
       <c r="D221">
-        <v>62.6</v>
+        <v>66.72</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -51618,7 +51618,7 @@
         <v>466</v>
       </c>
       <c r="D222">
-        <v>15.71</v>
+        <v>15.39</v>
       </c>
       <c r="E222">
         <v>648847</v>
@@ -51741,7 +51741,7 @@
         <v>467</v>
       </c>
       <c r="D225">
-        <v>23.65</v>
+        <v>24.89</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -51782,7 +51782,7 @@
         <v>466</v>
       </c>
       <c r="D226">
-        <v>61.43</v>
+        <v>60.9</v>
       </c>
       <c r="E226">
         <v>163969</v>
@@ -52028,7 +52028,7 @@
         <v>467</v>
       </c>
       <c r="D232">
-        <v>60.9</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -52069,7 +52069,7 @@
         <v>466</v>
       </c>
       <c r="D233">
-        <v>71.87</v>
+        <v>77.75</v>
       </c>
       <c r="E233">
         <v>128434</v>
@@ -52192,7 +52192,7 @@
         <v>467</v>
       </c>
       <c r="D236">
-        <v>16.69</v>
+        <v>17.21</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -52233,7 +52233,7 @@
         <v>467</v>
       </c>
       <c r="D237">
-        <v>77.48999999999999</v>
+        <v>74.98</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -52274,7 +52274,7 @@
         <v>466</v>
       </c>
       <c r="D238">
-        <v>173.4</v>
+        <v>163.82</v>
       </c>
       <c r="E238">
         <v>60955</v>
@@ -52315,7 +52315,7 @@
         <v>466</v>
       </c>
       <c r="D239">
-        <v>24.29</v>
+        <v>24.25</v>
       </c>
       <c r="E239">
         <v>411784</v>
@@ -52520,7 +52520,7 @@
         <v>467</v>
       </c>
       <c r="D244">
-        <v>161.54</v>
+        <v>168.84</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -52561,7 +52561,7 @@
         <v>466</v>
       </c>
       <c r="D245">
-        <v>19.94</v>
+        <v>19.38</v>
       </c>
       <c r="E245">
         <v>515261</v>
@@ -52684,7 +52684,7 @@
         <v>467</v>
       </c>
       <c r="D248">
-        <v>24.77</v>
+        <v>23.82</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -52725,7 +52725,7 @@
         <v>467</v>
       </c>
       <c r="D249">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -52766,7 +52766,7 @@
         <v>466</v>
       </c>
       <c r="D250">
-        <v>25.96</v>
+        <v>24.42</v>
       </c>
       <c r="E250">
         <v>408917</v>
@@ -52807,7 +52807,7 @@
         <v>466</v>
       </c>
       <c r="D251">
-        <v>24.74</v>
+        <v>23.24</v>
       </c>
       <c r="E251">
         <v>429680</v>
@@ -52889,7 +52889,7 @@
         <v>467</v>
       </c>
       <c r="D253">
-        <v>34.77</v>
+        <v>34.81</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -52930,7 +52930,7 @@
         <v>466</v>
       </c>
       <c r="D254">
-        <v>125.26</v>
+        <v>124.48</v>
       </c>
       <c r="E254">
         <v>80219</v>
@@ -53053,7 +53053,7 @@
         <v>467</v>
       </c>
       <c r="D257">
-        <v>27.05</v>
+        <v>28.5</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -53094,7 +53094,7 @@
         <v>466</v>
       </c>
       <c r="D258">
-        <v>33.1</v>
+        <v>30.94</v>
       </c>
       <c r="E258">
         <v>322746</v>
@@ -53217,7 +53217,7 @@
         <v>467</v>
       </c>
       <c r="D261">
-        <v>31.54</v>
+        <v>29.69</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -53258,7 +53258,7 @@
         <v>466</v>
       </c>
       <c r="D262">
-        <v>31.54</v>
+        <v>29.69</v>
       </c>
       <c r="E262">
         <v>336334</v>
@@ -53381,7 +53381,7 @@
         <v>467</v>
       </c>
       <c r="D265">
-        <v>32.91</v>
+        <v>34.5</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -53422,7 +53422,7 @@
         <v>467</v>
       </c>
       <c r="D266">
-        <v>129.91</v>
+        <v>124.87</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -53463,7 +53463,7 @@
         <v>466</v>
       </c>
       <c r="D267">
-        <v>32.57</v>
+        <v>29.32</v>
       </c>
       <c r="E267">
         <v>340578</v>
@@ -53504,7 +53504,7 @@
         <v>466</v>
       </c>
       <c r="D268">
-        <v>137.41</v>
+        <v>136.06</v>
       </c>
       <c r="E268">
         <v>73392</v>
@@ -53586,7 +53586,7 @@
         <v>467</v>
       </c>
       <c r="D270">
-        <v>27.12</v>
+        <v>28.28</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -53627,7 +53627,7 @@
         <v>467</v>
       </c>
       <c r="D271">
-        <v>26.07</v>
+        <v>27.48</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>467</v>
       </c>
       <c r="D272">
-        <v>137.41</v>
+        <v>141.48</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -53709,7 +53709,7 @@
         <v>466</v>
       </c>
       <c r="D273">
-        <v>42.61</v>
+        <v>43.14</v>
       </c>
       <c r="E273">
         <v>231473</v>
@@ -53750,7 +53750,7 @@
         <v>466</v>
       </c>
       <c r="D274">
-        <v>29.96</v>
+        <v>30.26</v>
       </c>
       <c r="E274">
         <v>329999</v>
@@ -53791,7 +53791,7 @@
         <v>466</v>
       </c>
       <c r="D275">
-        <v>621</v>
+        <v>598.45</v>
       </c>
       <c r="E275">
         <v>16686</v>
@@ -53832,7 +53832,7 @@
         <v>467</v>
       </c>
       <c r="D276">
-        <v>38.62</v>
+        <v>37.71</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -53873,7 +53873,7 @@
         <v>467</v>
       </c>
       <c r="D277">
-        <v>537.74</v>
+        <v>562.89</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -53955,7 +53955,7 @@
         <v>466</v>
       </c>
       <c r="D279">
-        <v>38.32</v>
+        <v>39.67</v>
       </c>
       <c r="E279">
         <v>251720</v>
@@ -53996,7 +53996,7 @@
         <v>466</v>
       </c>
       <c r="D280">
-        <v>1781.63</v>
+        <v>1807.33</v>
       </c>
       <c r="E280">
         <v>5525</v>
@@ -54037,7 +54037,7 @@
         <v>466</v>
       </c>
       <c r="D281">
-        <v>562.89</v>
+        <v>584.5700000000001</v>
       </c>
       <c r="E281">
         <v>17082</v>
@@ -54078,7 +54078,7 @@
         <v>467</v>
       </c>
       <c r="D282">
-        <v>1683.13</v>
+        <v>1691.69</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -54119,7 +54119,7 @@
         <v>467</v>
       </c>
       <c r="D283">
-        <v>613.1900000000001</v>
+        <v>616.66</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -54160,7 +54160,7 @@
         <v>467</v>
       </c>
       <c r="D284">
-        <v>43.9</v>
+        <v>43.14</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -54201,7 +54201,7 @@
         <v>466</v>
       </c>
       <c r="D285">
-        <v>358.34</v>
+        <v>347.8</v>
       </c>
       <c r="E285">
         <v>28711</v>
@@ -54242,7 +54242,7 @@
         <v>466</v>
       </c>
       <c r="D286">
-        <v>32.06</v>
+        <v>31.54</v>
       </c>
       <c r="E286">
         <v>316606</v>
@@ -54283,7 +54283,7 @@
         <v>466</v>
       </c>
       <c r="D287">
-        <v>90.93000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="E287">
         <v>113681</v>
@@ -54324,7 +54324,7 @@
         <v>467</v>
       </c>
       <c r="D288">
-        <v>312.23</v>
+        <v>325.07</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -54365,7 +54365,7 @@
         <v>467</v>
       </c>
       <c r="D289">
-        <v>80.09999999999999</v>
+        <v>82.03</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -54406,7 +54406,7 @@
         <v>466</v>
       </c>
       <c r="D290">
-        <v>312.23</v>
+        <v>325.07</v>
       </c>
       <c r="E290">
         <v>30718</v>
@@ -54447,7 +54447,7 @@
         <v>466</v>
       </c>
       <c r="D291">
-        <v>845.91</v>
+        <v>838.26</v>
       </c>
       <c r="E291">
         <v>11912</v>
@@ -54652,7 +54652,7 @@
         <v>467</v>
       </c>
       <c r="D296">
-        <v>34.33</v>
+        <v>35.65</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -54693,7 +54693,7 @@
         <v>466</v>
       </c>
       <c r="D297">
-        <v>42.01</v>
+        <v>41.86</v>
       </c>
       <c r="E297">
         <v>238551</v>
@@ -54939,7 +54939,7 @@
         <v>467</v>
       </c>
       <c r="D303">
-        <v>44.54</v>
+        <v>44.93</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -54980,7 +54980,7 @@
         <v>467</v>
       </c>
       <c r="D304">
-        <v>869.8</v>
+        <v>879.36</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -55021,7 +55021,7 @@
         <v>466</v>
       </c>
       <c r="D305">
-        <v>66.08</v>
+        <v>64.78</v>
       </c>
       <c r="E305">
         <v>154148</v>
@@ -55062,7 +55062,7 @@
         <v>466</v>
       </c>
       <c r="D306">
-        <v>388.04</v>
+        <v>392.78</v>
       </c>
       <c r="E306">
         <v>25423</v>
@@ -55144,7 +55144,7 @@
         <v>467</v>
       </c>
       <c r="D308">
-        <v>374.21</v>
+        <v>386.46</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -55185,7 +55185,7 @@
         <v>467</v>
       </c>
       <c r="D309">
-        <v>61.36</v>
+        <v>63.56</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -55226,7 +55226,7 @@
         <v>466</v>
       </c>
       <c r="D310">
-        <v>51.28</v>
+        <v>50.51</v>
       </c>
       <c r="E310">
         <v>197698</v>
@@ -55267,7 +55267,7 @@
         <v>466</v>
       </c>
       <c r="D311">
-        <v>44.47</v>
+        <v>45.08</v>
       </c>
       <c r="E311">
         <v>221512</v>
@@ -55349,7 +55349,7 @@
         <v>467</v>
       </c>
       <c r="D313">
-        <v>387.32</v>
+        <v>404.45</v>
       </c>
       <c r="E313">
         <v>0</v>
@@ -55390,7 +55390,7 @@
         <v>467</v>
       </c>
       <c r="D314">
-        <v>45.23</v>
+        <v>46</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -55431,7 +55431,7 @@
         <v>466</v>
       </c>
       <c r="D315">
-        <v>53.79</v>
+        <v>51.41</v>
       </c>
       <c r="E315">
         <v>194237</v>
@@ -55472,7 +55472,7 @@
         <v>466</v>
       </c>
       <c r="D316">
-        <v>32.53</v>
+        <v>31.86</v>
       </c>
       <c r="E316">
         <v>313426</v>
@@ -55554,7 +55554,7 @@
         <v>467</v>
       </c>
       <c r="D318">
-        <v>32.24</v>
+        <v>30.31</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -55595,7 +55595,7 @@
         <v>466</v>
       </c>
       <c r="D319">
-        <v>96.64</v>
+        <v>90.25</v>
       </c>
       <c r="E319">
         <v>110645</v>
@@ -55718,7 +55718,7 @@
         <v>467</v>
       </c>
       <c r="D322">
-        <v>57.3</v>
+        <v>57.99</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -55759,7 +55759,7 @@
         <v>467</v>
       </c>
       <c r="D323">
-        <v>66.77</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -55800,7 +55800,7 @@
         <v>467</v>
       </c>
       <c r="D324">
-        <v>81.87</v>
+        <v>82.27</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -55841,7 +55841,7 @@
         <v>466</v>
       </c>
       <c r="D325">
-        <v>81.84</v>
+        <v>73.7</v>
       </c>
       <c r="E325">
         <v>135492</v>
@@ -55882,7 +55882,7 @@
         <v>466</v>
       </c>
       <c r="D326">
-        <v>61.88</v>
+        <v>55.74</v>
       </c>
       <c r="E326">
         <v>179149</v>
@@ -55923,7 +55923,7 @@
         <v>466</v>
       </c>
       <c r="D327">
-        <v>35.12</v>
+        <v>32.07</v>
       </c>
       <c r="E327">
         <v>311374</v>
@@ -55964,7 +55964,7 @@
         <v>467</v>
       </c>
       <c r="D328">
-        <v>50.22</v>
+        <v>51.16</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -56005,7 +56005,7 @@
         <v>467</v>
       </c>
       <c r="D329">
-        <v>66.34</v>
+        <v>60.01</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -56046,7 +56046,7 @@
         <v>467</v>
       </c>
       <c r="D330">
-        <v>29.14</v>
+        <v>26.47</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -56087,7 +56087,7 @@
         <v>466</v>
       </c>
       <c r="D331">
-        <v>65.31999999999999</v>
+        <v>65.91</v>
       </c>
       <c r="E331">
         <v>151506</v>
@@ -56128,7 +56128,7 @@
         <v>466</v>
       </c>
       <c r="D332">
-        <v>59.31</v>
+        <v>65.2</v>
       </c>
       <c r="E332">
         <v>153155</v>
@@ -56169,7 +56169,7 @@
         <v>466</v>
       </c>
       <c r="D333">
-        <v>31.61</v>
+        <v>29.39</v>
       </c>
       <c r="E333">
         <v>339767</v>
@@ -56210,7 +56210,7 @@
         <v>467</v>
       </c>
       <c r="D334">
-        <v>28.93</v>
+        <v>30.56</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -56251,7 +56251,7 @@
         <v>466</v>
       </c>
       <c r="D335">
-        <v>66.25</v>
+        <v>65.92</v>
       </c>
       <c r="E335">
         <v>151483</v>
@@ -56374,7 +56374,7 @@
         <v>467</v>
       </c>
       <c r="D338">
-        <v>62.09</v>
+        <v>62.25</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -56415,7 +56415,7 @@
         <v>466</v>
       </c>
       <c r="D339">
-        <v>31.82</v>
+        <v>31.19</v>
       </c>
       <c r="E339">
         <v>320159</v>
@@ -56661,7 +56661,7 @@
         <v>467</v>
       </c>
       <c r="D345">
-        <v>141.69</v>
+        <v>155.8</v>
       </c>
       <c r="E345">
         <v>0</v>
@@ -56702,7 +56702,7 @@
         <v>467</v>
       </c>
       <c r="D346">
-        <v>29.6</v>
+        <v>29.94</v>
       </c>
       <c r="E346">
         <v>0</v>
@@ -56743,7 +56743,7 @@
         <v>467</v>
       </c>
       <c r="D347">
-        <v>118.56</v>
+        <v>130.12</v>
       </c>
       <c r="E347">
         <v>0</v>
@@ -56784,7 +56784,7 @@
         <v>466</v>
       </c>
       <c r="D348">
-        <v>141.69</v>
+        <v>155.8</v>
       </c>
       <c r="E348">
         <v>64093</v>
@@ -56825,7 +56825,7 @@
         <v>466</v>
       </c>
       <c r="D349">
-        <v>118.56</v>
+        <v>130.12</v>
       </c>
       <c r="E349">
         <v>76742</v>
@@ -56907,7 +56907,7 @@
         <v>467</v>
       </c>
       <c r="D351">
-        <v>1253.55</v>
+        <v>1239.19</v>
       </c>
       <c r="E351">
         <v>0</v>
@@ -56948,7 +56948,7 @@
         <v>466</v>
       </c>
       <c r="D352">
-        <v>1253.55</v>
+        <v>1306.18</v>
       </c>
       <c r="E352">
         <v>7645</v>
@@ -57071,7 +57071,7 @@
         <v>467</v>
       </c>
       <c r="D355">
-        <v>189.34</v>
+        <v>185.58</v>
       </c>
       <c r="E355">
         <v>0</v>
@@ -57112,7 +57112,7 @@
         <v>467</v>
       </c>
       <c r="D356">
-        <v>172.92</v>
+        <v>177.63</v>
       </c>
       <c r="E356">
         <v>0</v>
@@ -57153,7 +57153,7 @@
         <v>467</v>
       </c>
       <c r="D357">
-        <v>1310.96</v>
+        <v>1430.58</v>
       </c>
       <c r="E357">
         <v>0</v>
@@ -57194,7 +57194,7 @@
         <v>466</v>
       </c>
       <c r="D358">
-        <v>172.41</v>
+        <v>179.94</v>
       </c>
       <c r="E358">
         <v>55494</v>
@@ -57235,7 +57235,7 @@
         <v>466</v>
       </c>
       <c r="D359">
-        <v>160.08</v>
+        <v>156.65</v>
       </c>
       <c r="E359">
         <v>63745</v>
@@ -57276,7 +57276,7 @@
         <v>466</v>
       </c>
       <c r="D360">
-        <v>76.69</v>
+        <v>82.7</v>
       </c>
       <c r="E360">
         <v>120746</v>
@@ -57317,7 +57317,7 @@
         <v>467</v>
       </c>
       <c r="D361">
-        <v>162.07</v>
+        <v>158.94</v>
       </c>
       <c r="E361">
         <v>0</v>
@@ -57358,7 +57358,7 @@
         <v>467</v>
       </c>
       <c r="D362">
-        <v>141.25</v>
+        <v>127.12</v>
       </c>
       <c r="E362">
         <v>0</v>
@@ -57399,7 +57399,7 @@
         <v>467</v>
       </c>
       <c r="D363">
-        <v>70.09</v>
+        <v>73.98</v>
       </c>
       <c r="E363">
         <v>0</v>
@@ -57440,7 +57440,7 @@
         <v>466</v>
       </c>
       <c r="D364">
-        <v>179.31</v>
+        <v>163.32</v>
       </c>
       <c r="E364">
         <v>61142</v>
@@ -57481,7 +57481,7 @@
         <v>466</v>
       </c>
       <c r="D365">
-        <v>159.22</v>
+        <v>145.1</v>
       </c>
       <c r="E365">
         <v>68819</v>
@@ -57522,7 +57522,7 @@
         <v>466</v>
       </c>
       <c r="D366">
-        <v>72.03</v>
+        <v>76.52</v>
       </c>
       <c r="E366">
         <v>130498</v>
@@ -57563,7 +57563,7 @@
         <v>467</v>
       </c>
       <c r="D367">
-        <v>122.84</v>
+        <v>131.83</v>
       </c>
       <c r="E367">
         <v>0</v>
@@ -57604,7 +57604,7 @@
         <v>467</v>
       </c>
       <c r="D368">
-        <v>135.74</v>
+        <v>128.53</v>
       </c>
       <c r="E368">
         <v>0</v>
@@ -57645,7 +57645,7 @@
         <v>467</v>
       </c>
       <c r="D369">
-        <v>67.55</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="E369">
         <v>0</v>
@@ -57686,7 +57686,7 @@
         <v>466</v>
       </c>
       <c r="D370">
-        <v>128.53</v>
+        <v>141.38</v>
       </c>
       <c r="E370">
         <v>70630</v>
@@ -57727,7 +57727,7 @@
         <v>466</v>
       </c>
       <c r="D371">
-        <v>67.55</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="E371">
         <v>153603</v>
@@ -57768,7 +57768,7 @@
         <v>466</v>
       </c>
       <c r="D372">
-        <v>32.84</v>
+        <v>33.37</v>
       </c>
       <c r="E372">
         <v>299243</v>
@@ -57809,7 +57809,7 @@
         <v>467</v>
       </c>
       <c r="D373">
-        <v>140.13</v>
+        <v>145.46</v>
       </c>
       <c r="E373">
         <v>0</v>
@@ -57850,7 +57850,7 @@
         <v>467</v>
       </c>
       <c r="D374">
-        <v>34.08</v>
+        <v>35.59</v>
       </c>
       <c r="E374">
         <v>0</v>
@@ -57891,7 +57891,7 @@
         <v>466</v>
       </c>
       <c r="D375">
-        <v>146.08</v>
+        <v>138.56</v>
       </c>
       <c r="E375">
         <v>72068</v>
@@ -57932,7 +57932,7 @@
         <v>466</v>
       </c>
       <c r="D376">
-        <v>122.84</v>
+        <v>118.56</v>
       </c>
       <c r="E376">
         <v>84225</v>
@@ -58014,7 +58014,7 @@
         <v>467</v>
       </c>
       <c r="D378">
-        <v>63.91</v>
+        <v>64.84</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -58055,7 +58055,7 @@
         <v>467</v>
       </c>
       <c r="D379">
-        <v>117.28</v>
+        <v>111.71</v>
       </c>
       <c r="E379">
         <v>0</v>
@@ -58096,7 +58096,7 @@
         <v>466</v>
       </c>
       <c r="D380">
-        <v>64.84</v>
+        <v>62.13</v>
       </c>
       <c r="E380">
         <v>160723</v>
@@ -58137,7 +58137,7 @@
         <v>466</v>
       </c>
       <c r="D381">
-        <v>32.57</v>
+        <v>31.59</v>
       </c>
       <c r="E381">
         <v>316105</v>
@@ -58219,7 +58219,7 @@
         <v>467</v>
       </c>
       <c r="D383">
-        <v>128.84</v>
+        <v>141.69</v>
       </c>
       <c r="E383">
         <v>0</v>
@@ -58260,7 +58260,7 @@
         <v>466</v>
       </c>
       <c r="D384">
-        <v>139.68</v>
+        <v>141.89</v>
       </c>
       <c r="E384">
         <v>70376</v>
@@ -58383,7 +58383,7 @@
         <v>467</v>
       </c>
       <c r="D387">
-        <v>128.59</v>
+        <v>135.24</v>
       </c>
       <c r="E387">
         <v>0</v>
@@ -58424,7 +58424,7 @@
         <v>466</v>
       </c>
       <c r="D388">
-        <v>54.97</v>
+        <v>56.22</v>
       </c>
       <c r="E388">
         <v>177619</v>
@@ -58547,7 +58547,7 @@
         <v>467</v>
       </c>
       <c r="D391">
-        <v>59.57</v>
+        <v>59.91</v>
       </c>
       <c r="E391">
         <v>0</v>
@@ -58588,7 +58588,7 @@
         <v>467</v>
       </c>
       <c r="D392">
-        <v>34.58</v>
+        <v>34.25</v>
       </c>
       <c r="E392">
         <v>0</v>
@@ -58629,7 +58629,7 @@
         <v>466</v>
       </c>
       <c r="D393">
-        <v>34.25</v>
+        <v>32.9</v>
       </c>
       <c r="E393">
         <v>303518</v>
@@ -58670,7 +58670,7 @@
         <v>466</v>
       </c>
       <c r="D394">
-        <v>141.11</v>
+        <v>130</v>
       </c>
       <c r="E394">
         <v>76813</v>
@@ -58752,7 +58752,7 @@
         <v>467</v>
       </c>
       <c r="D396">
-        <v>49.33</v>
+        <v>51.99</v>
       </c>
       <c r="E396">
         <v>0</v>
@@ -58793,7 +58793,7 @@
         <v>467</v>
       </c>
       <c r="D397">
-        <v>130.41</v>
+        <v>129.18</v>
       </c>
       <c r="E397">
         <v>0</v>
@@ -58834,7 +58834,7 @@
         <v>467</v>
       </c>
       <c r="D398">
-        <v>33</v>
+        <v>32.67</v>
       </c>
       <c r="E398">
         <v>0</v>
@@ -58875,7 +58875,7 @@
         <v>466</v>
       </c>
       <c r="D399">
-        <v>214.21</v>
+        <v>207.64</v>
       </c>
       <c r="E399">
         <v>48091</v>
@@ -58916,7 +58916,7 @@
         <v>466</v>
       </c>
       <c r="D400">
-        <v>50.35</v>
+        <v>49.94</v>
       </c>
       <c r="E400">
         <v>199955</v>
@@ -58957,7 +58957,7 @@
         <v>466</v>
       </c>
       <c r="D401">
-        <v>1781.14</v>
+        <v>1776.33</v>
       </c>
       <c r="E401">
         <v>5621</v>
@@ -58998,7 +58998,7 @@
         <v>467</v>
       </c>
       <c r="D402">
-        <v>191.01</v>
+        <v>190.24</v>
       </c>
       <c r="E402">
         <v>0</v>
@@ -59039,7 +59039,7 @@
         <v>467</v>
       </c>
       <c r="D403">
-        <v>48.89</v>
+        <v>48.97</v>
       </c>
       <c r="E403">
         <v>0</v>
@@ -59080,7 +59080,7 @@
         <v>466</v>
       </c>
       <c r="D404">
-        <v>869.61</v>
+        <v>866.71</v>
       </c>
       <c r="E404">
         <v>11521</v>
@@ -59121,7 +59121,7 @@
         <v>466</v>
       </c>
       <c r="D405">
-        <v>127.12</v>
+        <v>127.94</v>
       </c>
       <c r="E405">
         <v>78050</v>
@@ -59203,7 +59203,7 @@
         <v>467</v>
       </c>
       <c r="D407">
-        <v>772.23</v>
+        <v>835.86</v>
       </c>
       <c r="E407">
         <v>0</v>
@@ -59244,7 +59244,7 @@
         <v>466</v>
       </c>
       <c r="D408">
-        <v>835.86</v>
+        <v>845.5</v>
       </c>
       <c r="E408">
         <v>11810</v>
@@ -59367,7 +59367,7 @@
         <v>467</v>
       </c>
       <c r="D411">
-        <v>116.01</v>
+        <v>113.54</v>
       </c>
       <c r="E411">
         <v>0</v>
@@ -59408,7 +59408,7 @@
         <v>467</v>
       </c>
       <c r="D412">
-        <v>2017.03</v>
+        <v>1964.07</v>
       </c>
       <c r="E412">
         <v>0</v>
@@ -59449,7 +59449,7 @@
         <v>466</v>
       </c>
       <c r="D413">
-        <v>1964.07</v>
+        <v>1935.19</v>
       </c>
       <c r="E413">
         <v>5160</v>
@@ -59490,7 +59490,7 @@
         <v>466</v>
       </c>
       <c r="D414">
-        <v>115.6</v>
+        <v>118.48</v>
       </c>
       <c r="E414">
         <v>84282</v>
@@ -59572,7 +59572,7 @@
         <v>467</v>
       </c>
       <c r="D416">
-        <v>118.07</v>
+        <v>116.01</v>
       </c>
       <c r="E416">
         <v>0</v>
@@ -59613,7 +59613,7 @@
         <v>466</v>
       </c>
       <c r="D417">
-        <v>84.59999999999999</v>
+        <v>84.87</v>
       </c>
       <c r="E417">
         <v>117659</v>
@@ -59982,7 +59982,7 @@
         <v>467</v>
       </c>
       <c r="D426">
-        <v>2339.56</v>
+        <v>2382.88</v>
       </c>
       <c r="E426">
         <v>0</v>
@@ -60023,7 +60023,7 @@
         <v>466</v>
       </c>
       <c r="D427">
-        <v>73.78</v>
+        <v>73.12</v>
       </c>
       <c r="E427">
         <v>136566</v>
@@ -60146,7 +60146,7 @@
         <v>467</v>
       </c>
       <c r="D430">
-        <v>1103.88</v>
+        <v>1074.96</v>
       </c>
       <c r="E430">
         <v>0</v>
@@ -60187,7 +60187,7 @@
         <v>467</v>
       </c>
       <c r="D431">
-        <v>67.54000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="E431">
         <v>0</v>
@@ -60228,7 +60228,7 @@
         <v>466</v>
       </c>
       <c r="D432">
-        <v>114.52</v>
+        <v>107.6</v>
       </c>
       <c r="E432">
         <v>92804</v>
@@ -60269,7 +60269,7 @@
         <v>466</v>
       </c>
       <c r="D433">
-        <v>67.54000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="E433">
         <v>146247</v>
@@ -60392,7 +60392,7 @@
         <v>466</v>
       </c>
       <c r="D436">
-        <v>148.8</v>
+        <v>151.56</v>
       </c>
       <c r="E436">
         <v>65886</v>
@@ -60884,7 +60884,7 @@
         <v>467</v>
       </c>
       <c r="D448">
-        <v>68.61</v>
+        <v>68.2</v>
       </c>
       <c r="E448">
         <v>0</v>
@@ -60925,7 +60925,7 @@
         <v>467</v>
       </c>
       <c r="D449">
-        <v>174.06</v>
+        <v>186</v>
       </c>
       <c r="E449">
         <v>0</v>
@@ -60966,7 +60966,7 @@
         <v>466</v>
       </c>
       <c r="D450">
-        <v>174.06</v>
+        <v>186</v>
       </c>
       <c r="E450">
         <v>53686</v>
@@ -61007,7 +61007,7 @@
         <v>466</v>
       </c>
       <c r="D451">
-        <v>122.69</v>
+        <v>119.2</v>
       </c>
       <c r="E451">
         <v>83773</v>
@@ -61089,7 +61089,7 @@
         <v>467</v>
       </c>
       <c r="D453">
-        <v>167.63</v>
+        <v>168.09</v>
       </c>
       <c r="E453">
         <v>0</v>
@@ -61171,7 +61171,7 @@
         <v>466</v>
       </c>
       <c r="D455">
-        <v>178.66</v>
+        <v>180.49</v>
       </c>
       <c r="E455">
         <v>55325</v>
@@ -61294,7 +61294,7 @@
         <v>467</v>
       </c>
       <c r="D458">
-        <v>163.5</v>
+        <v>167.17</v>
       </c>
       <c r="E458">
         <v>0</v>
@@ -61335,7 +61335,7 @@
         <v>467</v>
       </c>
       <c r="D459">
-        <v>186.49</v>
+        <v>200.76</v>
       </c>
       <c r="E459">
         <v>0</v>
@@ -61376,7 +61376,7 @@
         <v>466</v>
       </c>
       <c r="D460">
-        <v>186.49</v>
+        <v>200.76</v>
       </c>
       <c r="E460">
         <v>49739</v>
@@ -61499,7 +61499,7 @@
         <v>467</v>
       </c>
       <c r="D463">
-        <v>16.23</v>
+        <v>16.15</v>
       </c>
       <c r="E463">
         <v>0</v>
@@ -61540,7 +61540,7 @@
         <v>466</v>
       </c>
       <c r="D464">
-        <v>98.75</v>
+        <v>98.28</v>
       </c>
       <c r="E464">
         <v>101605</v>
@@ -61663,7 +61663,7 @@
         <v>467</v>
       </c>
       <c r="D467">
-        <v>130.69</v>
+        <v>127.45</v>
       </c>
       <c r="E467">
         <v>0</v>
@@ -61704,7 +61704,7 @@
         <v>466</v>
       </c>
       <c r="D468">
-        <v>445.45</v>
+        <v>434.44</v>
       </c>
       <c r="E468">
         <v>22985</v>
@@ -61827,7 +61827,7 @@
         <v>467</v>
       </c>
       <c r="D471">
-        <v>440.37</v>
+        <v>447.14</v>
       </c>
       <c r="E471">
         <v>0</v>
@@ -61868,7 +61868,7 @@
         <v>466</v>
       </c>
       <c r="D472">
-        <v>73.04000000000001</v>
+        <v>76.72</v>
       </c>
       <c r="E472">
         <v>130158</v>
@@ -61991,7 +61991,7 @@
         <v>467</v>
       </c>
       <c r="D475">
-        <v>213.65</v>
+        <v>201.22</v>
       </c>
       <c r="E475">
         <v>0</v>
@@ -62032,7 +62032,7 @@
         <v>467</v>
       </c>
       <c r="D476">
-        <v>68.67</v>
+        <v>75.52</v>
       </c>
       <c r="E476">
         <v>0</v>
@@ -62073,7 +62073,7 @@
         <v>466</v>
       </c>
       <c r="D477">
-        <v>75.44</v>
+        <v>69.61</v>
       </c>
       <c r="E477">
         <v>143453</v>
@@ -62114,7 +62114,7 @@
         <v>466</v>
       </c>
       <c r="D478">
-        <v>274.81</v>
+        <v>277.48</v>
       </c>
       <c r="E478">
         <v>35987</v>
@@ -62237,7 +62237,7 @@
         <v>466</v>
       </c>
       <c r="D481">
-        <v>102.47</v>
+        <v>104.8</v>
       </c>
       <c r="E481">
         <v>95284</v>
@@ -62360,7 +62360,7 @@
         <v>467</v>
       </c>
       <c r="D484">
-        <v>261.47</v>
+        <v>270.81</v>
       </c>
       <c r="E484">
         <v>0</v>
@@ -62401,7 +62401,7 @@
         <v>466</v>
       </c>
       <c r="D485">
-        <v>167.63</v>
+        <v>165.78</v>
       </c>
       <c r="E485">
         <v>60235</v>
@@ -62524,7 +62524,7 @@
         <v>467</v>
       </c>
       <c r="D488">
-        <v>76.81</v>
+        <v>73.64</v>
       </c>
       <c r="E488">
         <v>0</v>
@@ -62565,7 +62565,7 @@
         <v>467</v>
       </c>
       <c r="D489">
-        <v>155.16</v>
+        <v>161.17</v>
       </c>
       <c r="E489">
         <v>0</v>
@@ -62606,7 +62606,7 @@
         <v>466</v>
       </c>
       <c r="D490">
-        <v>21.9</v>
+        <v>22.88</v>
       </c>
       <c r="E490">
         <v>436441</v>
@@ -62647,7 +62647,7 @@
         <v>466</v>
       </c>
       <c r="D491">
-        <v>35.85</v>
+        <v>36.05</v>
       </c>
       <c r="E491">
         <v>276997</v>
@@ -62729,7 +62729,7 @@
         <v>467</v>
       </c>
       <c r="D493">
-        <v>99.20999999999999</v>
+        <v>98.28</v>
       </c>
       <c r="E493">
         <v>0</v>
@@ -62770,7 +62770,7 @@
         <v>467</v>
       </c>
       <c r="D494">
-        <v>34.83</v>
+        <v>34.06</v>
       </c>
       <c r="E494">
         <v>0</v>
@@ -62811,7 +62811,7 @@
         <v>466</v>
       </c>
       <c r="D495">
-        <v>210.04</v>
+        <v>210.75</v>
       </c>
       <c r="E495">
         <v>47382</v>
@@ -62852,7 +62852,7 @@
         <v>466</v>
       </c>
       <c r="D496">
-        <v>75.27</v>
+        <v>76.38</v>
       </c>
       <c r="E496">
         <v>130738</v>
@@ -63057,7 +63057,7 @@
         <v>467</v>
       </c>
       <c r="D501">
-        <v>192.56</v>
+        <v>209.32</v>
       </c>
       <c r="E501">
         <v>0</v>
@@ -63098,7 +63098,7 @@
         <v>467</v>
       </c>
       <c r="D502">
-        <v>24.54</v>
+        <v>24.29</v>
       </c>
       <c r="E502">
         <v>0</v>
@@ -63139,7 +63139,7 @@
         <v>466</v>
       </c>
       <c r="D503">
-        <v>24.46</v>
+        <v>24.71</v>
       </c>
       <c r="E503">
         <v>404118</v>
@@ -63180,7 +63180,7 @@
         <v>466</v>
       </c>
       <c r="D504">
-        <v>179.73</v>
+        <v>181.87</v>
       </c>
       <c r="E504">
         <v>54906</v>
@@ -63262,7 +63262,7 @@
         <v>467</v>
       </c>
       <c r="D506">
-        <v>69.34999999999999</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="E506">
         <v>0</v>
@@ -63303,7 +63303,7 @@
         <v>467</v>
       </c>
       <c r="D507">
-        <v>165.82</v>
+        <v>161.9</v>
       </c>
       <c r="E507">
         <v>0</v>
@@ -63344,7 +63344,7 @@
         <v>466</v>
       </c>
       <c r="D508">
-        <v>68.98999999999999</v>
+        <v>69.84</v>
       </c>
       <c r="E508">
         <v>142980</v>
@@ -63385,7 +63385,7 @@
         <v>466</v>
       </c>
       <c r="D509">
-        <v>160.47</v>
+        <v>166.53</v>
       </c>
       <c r="E509">
         <v>59963</v>
@@ -63467,7 +63467,7 @@
         <v>467</v>
       </c>
       <c r="D511">
-        <v>70.52</v>
+        <v>69.16</v>
       </c>
       <c r="E511">
         <v>0</v>
@@ -63508,7 +63508,7 @@
         <v>467</v>
       </c>
       <c r="D512">
-        <v>157.62</v>
+        <v>161.18</v>
       </c>
       <c r="E512">
         <v>0</v>
@@ -63549,7 +63549,7 @@
         <v>466</v>
       </c>
       <c r="D513">
-        <v>185.18</v>
+        <v>179.64</v>
       </c>
       <c r="E513">
         <v>55587</v>
@@ -63590,7 +63590,7 @@
         <v>466</v>
       </c>
       <c r="D514">
-        <v>42.83</v>
+        <v>42.43</v>
       </c>
       <c r="E514">
         <v>235346</v>
@@ -63795,7 +63795,7 @@
         <v>467</v>
       </c>
       <c r="D519">
-        <v>25.61</v>
+        <v>25.52</v>
       </c>
       <c r="E519">
         <v>0</v>
@@ -63836,7 +63836,7 @@
         <v>466</v>
       </c>
       <c r="D520">
-        <v>159.4</v>
+        <v>150.84</v>
       </c>
       <c r="E520">
         <v>66201</v>
@@ -63959,7 +63959,7 @@
         <v>467</v>
       </c>
       <c r="D523">
-        <v>45.49</v>
+        <v>44.18</v>
       </c>
       <c r="E523">
         <v>0</v>
@@ -64000,7 +64000,7 @@
         <v>467</v>
       </c>
       <c r="D524">
-        <v>185.64</v>
+        <v>188.87</v>
       </c>
       <c r="E524">
         <v>0</v>
@@ -64082,7 +64082,7 @@
         <v>466</v>
       </c>
       <c r="D526">
-        <v>224.75</v>
+        <v>210.85</v>
       </c>
       <c r="E526">
         <v>47359</v>
@@ -64123,7 +64123,7 @@
         <v>466</v>
       </c>
       <c r="D527">
-        <v>124.72</v>
+        <v>122.83</v>
       </c>
       <c r="E527">
         <v>81297</v>
@@ -64164,7 +64164,7 @@
         <v>466</v>
       </c>
       <c r="D528">
-        <v>24.71</v>
+        <v>23.78</v>
       </c>
       <c r="E528">
         <v>419923</v>
@@ -64205,7 +64205,7 @@
         <v>467</v>
       </c>
       <c r="D529">
-        <v>121.88</v>
+        <v>124.72</v>
       </c>
       <c r="E529">
         <v>0</v>
@@ -64246,7 +64246,7 @@
         <v>467</v>
       </c>
       <c r="D530">
-        <v>224.75</v>
+        <v>227.54</v>
       </c>
       <c r="E530">
         <v>0</v>
@@ -64287,7 +64287,7 @@
         <v>467</v>
       </c>
       <c r="D531">
-        <v>21.73</v>
+        <v>22.41</v>
       </c>
       <c r="E531">
         <v>0</v>
@@ -64328,7 +64328,7 @@
         <v>466</v>
       </c>
       <c r="D532">
-        <v>181.02</v>
+        <v>188.41</v>
       </c>
       <c r="E532">
         <v>53000</v>
@@ -64369,7 +64369,7 @@
         <v>466</v>
       </c>
       <c r="D533">
-        <v>71.95999999999999</v>
+        <v>71.37</v>
       </c>
       <c r="E533">
         <v>139915</v>
@@ -64410,7 +64410,7 @@
         <v>466</v>
       </c>
       <c r="D534">
-        <v>128.69</v>
+        <v>131.02</v>
       </c>
       <c r="E534">
         <v>76215</v>
@@ -64451,7 +64451,7 @@
         <v>467</v>
       </c>
       <c r="D535">
-        <v>174.1</v>
+        <v>157.01</v>
       </c>
       <c r="E535">
         <v>0</v>
@@ -64615,7 +64615,7 @@
         <v>467</v>
       </c>
       <c r="D539">
-        <v>22.98</v>
+        <v>25.28</v>
       </c>
       <c r="E539">
         <v>0</v>
@@ -64656,7 +64656,7 @@
         <v>467</v>
       </c>
       <c r="D540">
-        <v>70.69</v>
+        <v>70.52</v>
       </c>
       <c r="E540">
         <v>0</v>
@@ -64697,7 +64697,7 @@
         <v>466</v>
       </c>
       <c r="D541">
-        <v>28.36</v>
+        <v>28.85</v>
       </c>
       <c r="E541">
         <v>346127</v>
@@ -64738,7 +64738,7 @@
         <v>466</v>
       </c>
       <c r="D542">
-        <v>1631.89</v>
+        <v>1654.12</v>
       </c>
       <c r="E542">
         <v>6036</v>
@@ -64820,7 +64820,7 @@
         <v>467</v>
       </c>
       <c r="D544">
-        <v>25.67</v>
+        <v>27.38</v>
       </c>
       <c r="E544">
         <v>0</v>
@@ -64861,7 +64861,7 @@
         <v>467</v>
       </c>
       <c r="D545">
-        <v>128.69</v>
+        <v>131.02</v>
       </c>
       <c r="E545">
         <v>0</v>
@@ -64902,7 +64902,7 @@
         <v>467</v>
       </c>
       <c r="D546">
-        <v>1707.48</v>
+        <v>1743.05</v>
       </c>
       <c r="E546">
         <v>0</v>
@@ -64943,7 +64943,7 @@
         <v>466</v>
       </c>
       <c r="D547">
-        <v>26.5</v>
+        <v>27.48</v>
       </c>
       <c r="E547">
         <v>363383</v>
@@ -64984,7 +64984,7 @@
         <v>466</v>
       </c>
       <c r="D548">
-        <v>297.79</v>
+        <v>318.26</v>
       </c>
       <c r="E548">
         <v>31376</v>
@@ -65025,7 +65025,7 @@
         <v>466</v>
       </c>
       <c r="D549">
-        <v>47.34</v>
+        <v>44.75</v>
       </c>
       <c r="E549">
         <v>223145</v>
@@ -65066,7 +65066,7 @@
         <v>467</v>
       </c>
       <c r="D550">
-        <v>281.57</v>
+        <v>306.75</v>
       </c>
       <c r="E550">
         <v>0</v>
@@ -65107,7 +65107,7 @@
         <v>467</v>
       </c>
       <c r="D551">
-        <v>47.07</v>
+        <v>46.53</v>
       </c>
       <c r="E551">
         <v>0</v>
@@ -65148,7 +65148,7 @@
         <v>466</v>
       </c>
       <c r="D552">
-        <v>84.44</v>
+        <v>85.3</v>
       </c>
       <c r="E552">
         <v>117066</v>
@@ -65189,7 +65189,7 @@
         <v>466</v>
       </c>
       <c r="D553">
-        <v>150.41</v>
+        <v>152.3</v>
       </c>
       <c r="E553">
         <v>65566</v>
@@ -65271,7 +65271,7 @@
         <v>467</v>
       </c>
       <c r="D555">
-        <v>26.01</v>
+        <v>27.28</v>
       </c>
       <c r="E555">
         <v>0</v>
@@ -65312,7 +65312,7 @@
         <v>467</v>
       </c>
       <c r="D556">
-        <v>72.52</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E556">
         <v>0</v>
@@ -65353,7 +65353,7 @@
         <v>467</v>
       </c>
       <c r="D557">
-        <v>153.72</v>
+        <v>160.81</v>
       </c>
       <c r="E557">
         <v>0</v>
@@ -65394,7 +65394,7 @@
         <v>466</v>
       </c>
       <c r="D558">
-        <v>29.97</v>
+        <v>32.96</v>
       </c>
       <c r="E558">
         <v>302966</v>
@@ -65435,7 +65435,7 @@
         <v>466</v>
       </c>
       <c r="D559">
-        <v>1867.56</v>
+        <v>1849.77</v>
       </c>
       <c r="E559">
         <v>5398</v>
@@ -65476,7 +65476,7 @@
         <v>466</v>
       </c>
       <c r="D560">
-        <v>304.61</v>
+        <v>306.75</v>
       </c>
       <c r="E560">
         <v>32553</v>
@@ -65517,7 +65517,7 @@
         <v>467</v>
       </c>
       <c r="D561">
-        <v>1840.88</v>
+        <v>1872</v>
       </c>
       <c r="E561">
         <v>0</v>
@@ -65558,7 +65558,7 @@
         <v>466</v>
       </c>
       <c r="D562">
-        <v>264.86</v>
+        <v>265.34</v>
       </c>
       <c r="E562">
         <v>37633</v>
@@ -65681,7 +65681,7 @@
         <v>467</v>
       </c>
       <c r="D565">
-        <v>261.54</v>
+        <v>259.64</v>
       </c>
       <c r="E565">
         <v>0</v>
@@ -65722,7 +65722,7 @@
         <v>466</v>
       </c>
       <c r="D566">
-        <v>102.17</v>
+        <v>112.34</v>
       </c>
       <c r="E566">
         <v>88888</v>
@@ -65968,7 +65968,7 @@
         <v>467</v>
       </c>
       <c r="D572">
-        <v>33.84</v>
+        <v>32.91</v>
       </c>
       <c r="E572">
         <v>0</v>
@@ -66009,7 +66009,7 @@
         <v>467</v>
       </c>
       <c r="D573">
-        <v>377.14</v>
+        <v>383.11</v>
       </c>
       <c r="E573">
         <v>0</v>
@@ -66050,7 +66050,7 @@
         <v>466</v>
       </c>
       <c r="D574">
-        <v>35.64</v>
+        <v>38.14</v>
       </c>
       <c r="E574">
         <v>261818</v>
@@ -66091,7 +66091,7 @@
         <v>466</v>
       </c>
       <c r="D575">
-        <v>286.9</v>
+        <v>285.04</v>
       </c>
       <c r="E575">
         <v>35032</v>
@@ -66173,7 +66173,7 @@
         <v>467</v>
       </c>
       <c r="D577">
-        <v>36.18</v>
+        <v>37.94</v>
       </c>
       <c r="E577">
         <v>0</v>
@@ -66214,7 +66214,7 @@
         <v>466</v>
       </c>
       <c r="D578">
-        <v>261.22</v>
+        <v>270.99</v>
       </c>
       <c r="E578">
         <v>36849</v>
@@ -66337,7 +66337,7 @@
         <v>467</v>
       </c>
       <c r="D581">
-        <v>113.67</v>
+        <v>113.22</v>
       </c>
       <c r="E581">
         <v>0</v>
@@ -66378,7 +66378,7 @@
         <v>467</v>
       </c>
       <c r="D582">
-        <v>247.25</v>
+        <v>260.29</v>
       </c>
       <c r="E582">
         <v>0</v>
@@ -66419,7 +66419,7 @@
         <v>466</v>
       </c>
       <c r="D583">
-        <v>260.29</v>
+        <v>249.11</v>
       </c>
       <c r="E583">
         <v>40085</v>
@@ -66460,7 +66460,7 @@
         <v>466</v>
       </c>
       <c r="D584">
-        <v>145.84</v>
+        <v>133.8</v>
       </c>
       <c r="E584">
         <v>74632</v>
@@ -66542,7 +66542,7 @@
         <v>467</v>
       </c>
       <c r="D586">
-        <v>255.27</v>
+        <v>253.78</v>
       </c>
       <c r="E586">
         <v>0</v>
@@ -66624,7 +66624,7 @@
         <v>466</v>
       </c>
       <c r="D588">
-        <v>15.69</v>
+        <v>14.64</v>
       </c>
       <c r="E588">
         <v>682088</v>
@@ -66665,7 +66665,7 @@
         <v>466</v>
       </c>
       <c r="D589">
-        <v>282.44</v>
+        <v>292.86</v>
       </c>
       <c r="E589">
         <v>34097</v>
@@ -66747,7 +66747,7 @@
         <v>467</v>
       </c>
       <c r="D591">
-        <v>234.68</v>
+        <v>211.39</v>
       </c>
       <c r="E591">
         <v>0</v>
@@ -66788,7 +66788,7 @@
         <v>467</v>
       </c>
       <c r="D592">
-        <v>257.88</v>
+        <v>232.57</v>
       </c>
       <c r="E592">
         <v>0</v>
@@ -66829,7 +66829,7 @@
         <v>466</v>
       </c>
       <c r="D593">
-        <v>231.46</v>
+        <v>240.02</v>
       </c>
       <c r="E593">
         <v>41603</v>
@@ -66952,7 +66952,7 @@
         <v>467</v>
       </c>
       <c r="D596">
-        <v>216.94</v>
+        <v>226.99</v>
       </c>
       <c r="E596">
         <v>0</v>
@@ -66993,7 +66993,7 @@
         <v>466</v>
       </c>
       <c r="D597">
-        <v>27.7</v>
+        <v>27.78</v>
       </c>
       <c r="E597">
         <v>359458</v>
@@ -67116,7 +67116,7 @@
         <v>467</v>
       </c>
       <c r="D600">
-        <v>343.01</v>
+        <v>342.16</v>
       </c>
       <c r="E600">
         <v>0</v>
@@ -67157,7 +67157,7 @@
         <v>466</v>
       </c>
       <c r="D601">
-        <v>42.9</v>
+        <v>43.45</v>
       </c>
       <c r="E601">
         <v>229822</v>
@@ -67280,7 +67280,7 @@
         <v>467</v>
       </c>
       <c r="D604">
-        <v>45.76</v>
+        <v>44.75</v>
       </c>
       <c r="E604">
         <v>0</v>
@@ -67321,7 +67321,7 @@
         <v>467</v>
       </c>
       <c r="D605">
-        <v>28.66</v>
+        <v>28.4</v>
       </c>
       <c r="E605">
         <v>0</v>
@@ -67362,7 +67362,7 @@
         <v>466</v>
       </c>
       <c r="D606">
-        <v>287.65</v>
+        <v>288.02</v>
       </c>
       <c r="E606">
         <v>34670</v>
@@ -67403,7 +67403,7 @@
         <v>466</v>
       </c>
       <c r="D607">
-        <v>401.03</v>
+        <v>414.68</v>
       </c>
       <c r="E607">
         <v>24080</v>
@@ -67485,7 +67485,7 @@
         <v>467</v>
       </c>
       <c r="D609">
-        <v>418.1</v>
+        <v>406.15</v>
       </c>
       <c r="E609">
         <v>0</v>
@@ -67526,7 +67526,7 @@
         <v>467</v>
       </c>
       <c r="D610">
-        <v>313.7</v>
+        <v>342.35</v>
       </c>
       <c r="E610">
         <v>0</v>
@@ -67567,7 +67567,7 @@
         <v>466</v>
       </c>
       <c r="D611">
-        <v>79.51000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="E611">
         <v>129299</v>
@@ -67608,7 +67608,7 @@
         <v>466</v>
       </c>
       <c r="D612">
-        <v>47.79</v>
+        <v>47.61</v>
       </c>
       <c r="E612">
         <v>209741</v>
@@ -67690,7 +67690,7 @@
         <v>467</v>
       </c>
       <c r="D614">
-        <v>73.55</v>
+        <v>73.2</v>
       </c>
       <c r="E614">
         <v>0</v>
@@ -67731,7 +67731,7 @@
         <v>467</v>
       </c>
       <c r="D615">
-        <v>47.14</v>
+        <v>47.79</v>
       </c>
       <c r="E615">
         <v>0</v>
@@ -67772,7 +67772,7 @@
         <v>466</v>
       </c>
       <c r="D616">
-        <v>386.26</v>
+        <v>376.58</v>
       </c>
       <c r="E616">
         <v>26516</v>
@@ -67813,7 +67813,7 @@
         <v>466</v>
       </c>
       <c r="D617">
-        <v>105.05</v>
+        <v>103.65</v>
       </c>
       <c r="E617">
         <v>96341</v>
@@ -67895,7 +67895,7 @@
         <v>467</v>
       </c>
       <c r="D619">
-        <v>380.3</v>
+        <v>391.47</v>
       </c>
       <c r="E619">
         <v>0</v>
@@ -67936,7 +67936,7 @@
         <v>466</v>
       </c>
       <c r="D620">
-        <v>51.83</v>
+        <v>51.63</v>
       </c>
       <c r="E620">
         <v>193410</v>
@@ -68059,7 +68059,7 @@
         <v>467</v>
       </c>
       <c r="D623">
-        <v>108.78</v>
+        <v>110.18</v>
       </c>
       <c r="E623">
         <v>0</v>
@@ -68100,7 +68100,7 @@
         <v>466</v>
       </c>
       <c r="D624">
-        <v>49.64</v>
+        <v>50.84</v>
       </c>
       <c r="E624">
         <v>196415</v>
@@ -68223,7 +68223,7 @@
         <v>467</v>
       </c>
       <c r="D627">
-        <v>48.41</v>
+        <v>45.77</v>
       </c>
       <c r="E627">
         <v>0</v>
@@ -68264,7 +68264,7 @@
         <v>467</v>
       </c>
       <c r="D628">
-        <v>46.78</v>
+        <v>47.61</v>
       </c>
       <c r="E628">
         <v>0</v>
@@ -68305,7 +68305,7 @@
         <v>467</v>
       </c>
       <c r="D629">
-        <v>19.23</v>
+        <v>17.94</v>
       </c>
       <c r="E629">
         <v>0</v>
@@ -68346,7 +68346,7 @@
         <v>466</v>
       </c>
       <c r="D630">
-        <v>390.72</v>
+        <v>375.09</v>
       </c>
       <c r="E630">
         <v>26622</v>
@@ -68387,7 +68387,7 @@
         <v>466</v>
       </c>
       <c r="D631">
-        <v>146.23</v>
+        <v>154.81</v>
       </c>
       <c r="E631">
         <v>64503</v>
@@ -68428,7 +68428,7 @@
         <v>466</v>
       </c>
       <c r="D632">
-        <v>46.79</v>
+        <v>42.15</v>
       </c>
       <c r="E632">
         <v>236910</v>
@@ -68469,7 +68469,7 @@
         <v>467</v>
       </c>
       <c r="D633">
-        <v>39.07</v>
+        <v>38.92</v>
       </c>
       <c r="E633">
         <v>0</v>
@@ -68510,7 +68510,7 @@
         <v>466</v>
       </c>
       <c r="D634">
-        <v>107.38</v>
+        <v>105.05</v>
       </c>
       <c r="E634">
         <v>95057</v>
@@ -68633,7 +68633,7 @@
         <v>467</v>
       </c>
       <c r="D637">
-        <v>340.12</v>
+        <v>357.23</v>
       </c>
       <c r="E637">
         <v>0</v>
@@ -68674,7 +68674,7 @@
         <v>467</v>
       </c>
       <c r="D638">
-        <v>109.72</v>
+        <v>108.78</v>
       </c>
       <c r="E638">
         <v>0</v>
@@ -68715,7 +68715,7 @@
         <v>466</v>
       </c>
       <c r="D639">
-        <v>368.02</v>
+        <v>378.82</v>
       </c>
       <c r="E639">
         <v>26360</v>
@@ -68756,7 +68756,7 @@
         <v>466</v>
       </c>
       <c r="D640">
-        <v>54.16</v>
+        <v>53.88</v>
       </c>
       <c r="E640">
         <v>185333</v>
@@ -68838,7 +68838,7 @@
         <v>467</v>
       </c>
       <c r="D642">
-        <v>55.26</v>
+        <v>59.97</v>
       </c>
       <c r="E642">
         <v>0</v>
@@ -68879,7 +68879,7 @@
         <v>466</v>
       </c>
       <c r="D643">
-        <v>831.27</v>
+        <v>874.09</v>
       </c>
       <c r="E643">
         <v>11424</v>
@@ -69002,7 +69002,7 @@
         <v>467</v>
       </c>
       <c r="D646">
-        <v>879.6799999999999</v>
+        <v>923.4299999999999</v>
       </c>
       <c r="E646">
         <v>0</v>
@@ -69043,7 +69043,7 @@
         <v>467</v>
       </c>
       <c r="D647">
-        <v>391.47</v>
+        <v>398.17</v>
       </c>
       <c r="E647">
         <v>0</v>
@@ -69084,7 +69084,7 @@
         <v>466</v>
       </c>
       <c r="D648">
-        <v>47.48</v>
+        <v>48.31</v>
       </c>
       <c r="E648">
         <v>206701</v>
@@ -69125,7 +69125,7 @@
         <v>466</v>
       </c>
       <c r="D649">
-        <v>66.5</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="E649">
         <v>146935</v>
@@ -69207,7 +69207,7 @@
         <v>467</v>
       </c>
       <c r="D651">
-        <v>67.40000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="E651">
         <v>0</v>
@@ -69248,7 +69248,7 @@
         <v>466</v>
       </c>
       <c r="D652">
-        <v>427.94</v>
+        <v>423.47</v>
       </c>
       <c r="E652">
         <v>23580</v>
@@ -69371,7 +69371,7 @@
         <v>467</v>
       </c>
       <c r="D655">
-        <v>47.62</v>
+        <v>46.94</v>
       </c>
       <c r="E655">
         <v>0</v>
@@ -69412,7 +69412,7 @@
         <v>467</v>
       </c>
       <c r="D656">
-        <v>403.38</v>
+        <v>430.17</v>
       </c>
       <c r="E656">
         <v>0</v>
@@ -69494,7 +69494,7 @@
         <v>466</v>
       </c>
       <c r="D658">
-        <v>47.62</v>
+        <v>46.94</v>
       </c>
       <c r="E658">
         <v>212734</v>
@@ -69576,7 +69576,7 @@
         <v>467</v>
       </c>
       <c r="D660">
-        <v>48.02</v>
+        <v>49.78</v>
       </c>
       <c r="E660">
         <v>0</v>
@@ -69617,7 +69617,7 @@
         <v>467</v>
       </c>
       <c r="D661">
-        <v>179.68</v>
+        <v>177.11</v>
       </c>
       <c r="E661">
         <v>0</v>
@@ -69658,7 +69658,7 @@
         <v>466</v>
       </c>
       <c r="D662">
-        <v>252.13</v>
+        <v>249.01</v>
       </c>
       <c r="E662">
         <v>40101</v>
@@ -69699,7 +69699,7 @@
         <v>466</v>
       </c>
       <c r="D663">
-        <v>508.54</v>
+        <v>518.78</v>
       </c>
       <c r="E663">
         <v>19248</v>
@@ -69781,7 +69781,7 @@
         <v>467</v>
       </c>
       <c r="D665">
-        <v>496.6</v>
+        <v>498.3</v>
       </c>
       <c r="E665">
         <v>0</v>
@@ -69822,7 +69822,7 @@
         <v>466</v>
       </c>
       <c r="D666">
-        <v>60.43</v>
+        <v>59.69</v>
       </c>
       <c r="E666">
         <v>167293</v>
@@ -69945,7 +69945,7 @@
         <v>467</v>
       </c>
       <c r="D669">
-        <v>353.11</v>
+        <v>355.16</v>
       </c>
       <c r="E669">
         <v>0</v>
@@ -69986,7 +69986,7 @@
         <v>467</v>
       </c>
       <c r="D670">
-        <v>61.35</v>
+        <v>62.27</v>
       </c>
       <c r="E670">
         <v>0</v>
@@ -70027,7 +70027,7 @@
         <v>467</v>
       </c>
       <c r="D671">
-        <v>249.9</v>
+        <v>250.35</v>
       </c>
       <c r="E671">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>466</v>
       </c>
       <c r="D673">
-        <v>102.91</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E673">
         <v>100067</v>
@@ -70150,7 +70150,7 @@
         <v>466</v>
       </c>
       <c r="D674">
-        <v>2709.99</v>
+        <v>2777.74</v>
       </c>
       <c r="E674">
         <v>3594</v>
@@ -70191,7 +70191,7 @@
         <v>467</v>
       </c>
       <c r="D675">
-        <v>89.98999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="E675">
         <v>0</v>
@@ -70232,7 +70232,7 @@
         <v>467</v>
       </c>
       <c r="D676">
-        <v>1151.48</v>
+        <v>1210.03</v>
       </c>
       <c r="E676">
         <v>0</v>
@@ -70273,7 +70273,7 @@
         <v>466</v>
       </c>
       <c r="D677">
-        <v>270.7</v>
+        <v>263.16</v>
       </c>
       <c r="E677">
         <v>37945</v>
@@ -70314,7 +70314,7 @@
         <v>466</v>
       </c>
       <c r="D678">
-        <v>1151.48</v>
+        <v>1210.03</v>
       </c>
       <c r="E678">
         <v>8252</v>
@@ -70396,7 +70396,7 @@
         <v>467</v>
       </c>
       <c r="D680">
-        <v>2550.29</v>
+        <v>2516.42</v>
       </c>
       <c r="E680">
         <v>0</v>
@@ -70437,7 +70437,7 @@
         <v>467</v>
       </c>
       <c r="D681">
-        <v>1307.61</v>
+        <v>1258.82</v>
       </c>
       <c r="E681">
         <v>0</v>
@@ -70478,7 +70478,7 @@
         <v>466</v>
       </c>
       <c r="D682">
-        <v>42.84</v>
+        <v>41.5</v>
       </c>
       <c r="E682">
         <v>240620</v>
@@ -70519,7 +70519,7 @@
         <v>466</v>
       </c>
       <c r="D683">
-        <v>51.22</v>
+        <v>51.3</v>
       </c>
       <c r="E683">
         <v>194654</v>
@@ -70601,7 +70601,7 @@
         <v>467</v>
       </c>
       <c r="D685">
-        <v>49.09</v>
+        <v>46.28</v>
       </c>
       <c r="E685">
         <v>0</v>
@@ -70642,7 +70642,7 @@
         <v>466</v>
       </c>
       <c r="D686">
-        <v>228.23</v>
+        <v>221.06</v>
       </c>
       <c r="E686">
         <v>45172</v>
@@ -70765,7 +70765,7 @@
         <v>467</v>
       </c>
       <c r="D689">
-        <v>44.52</v>
+        <v>45.91</v>
       </c>
       <c r="E689">
         <v>0</v>
@@ -70806,7 +70806,7 @@
         <v>467</v>
       </c>
       <c r="D690">
-        <v>239.69</v>
+        <v>242.2</v>
       </c>
       <c r="E690">
         <v>0</v>
@@ -70847,7 +70847,7 @@
         <v>466</v>
       </c>
       <c r="D691">
-        <v>47.03</v>
+        <v>49.19</v>
       </c>
       <c r="E691">
         <v>203004</v>
@@ -70888,7 +70888,7 @@
         <v>466</v>
       </c>
       <c r="D692">
-        <v>38.16</v>
+        <v>35.02</v>
       </c>
       <c r="E692">
         <v>285144</v>
@@ -70970,7 +70970,7 @@
         <v>467</v>
       </c>
       <c r="D694">
-        <v>34.33</v>
+        <v>32.95</v>
       </c>
       <c r="E694">
         <v>0</v>
@@ -71011,7 +71011,7 @@
         <v>467</v>
       </c>
       <c r="D695">
-        <v>243.98</v>
+        <v>239.69</v>
       </c>
       <c r="E695">
         <v>0</v>
@@ -71052,7 +71052,7 @@
         <v>466</v>
       </c>
       <c r="D696">
-        <v>176.98</v>
+        <v>172.63</v>
       </c>
       <c r="E696">
         <v>57844</v>
@@ -71093,7 +71093,7 @@
         <v>466</v>
       </c>
       <c r="D697">
-        <v>46.04</v>
+        <v>44.29</v>
       </c>
       <c r="E697">
         <v>225463</v>
@@ -71175,7 +71175,7 @@
         <v>467</v>
       </c>
       <c r="D699">
-        <v>172.14</v>
+        <v>179.88</v>
       </c>
       <c r="E699">
         <v>0</v>
@@ -71216,7 +71216,7 @@
         <v>467</v>
       </c>
       <c r="D700">
-        <v>45.53</v>
+        <v>46.59</v>
       </c>
       <c r="E700">
         <v>0</v>
@@ -71257,7 +71257,7 @@
         <v>466</v>
       </c>
       <c r="D701">
-        <v>1410.07</v>
+        <v>1405.19</v>
       </c>
       <c r="E701">
         <v>7106</v>
@@ -71298,7 +71298,7 @@
         <v>466</v>
       </c>
       <c r="D702">
-        <v>37.72</v>
+        <v>41.46</v>
       </c>
       <c r="E702">
         <v>240853</v>
@@ -71380,7 +71380,7 @@
         <v>467</v>
       </c>
       <c r="D704">
-        <v>39.39</v>
+        <v>40.43</v>
       </c>
       <c r="E704">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>467</v>
       </c>
       <c r="D705">
-        <v>1522.29</v>
+        <v>1473.5</v>
       </c>
       <c r="E705">
         <v>0</v>
@@ -71462,7 +71462,7 @@
         <v>466</v>
       </c>
       <c r="D706">
-        <v>56.81</v>
+        <v>59.85</v>
       </c>
       <c r="E706">
         <v>166846</v>
@@ -71503,7 +71503,7 @@
         <v>466</v>
       </c>
       <c r="D707">
-        <v>261.65</v>
+        <v>266.42</v>
       </c>
       <c r="E707">
         <v>37481</v>
@@ -71585,7 +71585,7 @@
         <v>467</v>
       </c>
       <c r="D709">
-        <v>51.78</v>
+        <v>54.12</v>
       </c>
       <c r="E709">
         <v>0</v>
@@ -71626,7 +71626,7 @@
         <v>467</v>
       </c>
       <c r="D710">
-        <v>272.63</v>
+        <v>267.38</v>
       </c>
       <c r="E710">
         <v>0</v>
@@ -71667,7 +71667,7 @@
         <v>466</v>
       </c>
       <c r="D711">
-        <v>500.35</v>
+        <v>492.77</v>
       </c>
       <c r="E711">
         <v>20264</v>
@@ -71708,7 +71708,7 @@
         <v>466</v>
       </c>
       <c r="D712">
-        <v>45.44</v>
+        <v>47.61</v>
       </c>
       <c r="E712">
         <v>209741</v>
@@ -71790,7 +71790,7 @@
         <v>467</v>
       </c>
       <c r="D714">
-        <v>494.67</v>
+        <v>502.25</v>
       </c>
       <c r="E714">
         <v>0</v>
@@ -71831,7 +71831,7 @@
         <v>467</v>
       </c>
       <c r="D715">
-        <v>43.28</v>
+        <v>45.89</v>
       </c>
       <c r="E715">
         <v>0</v>
@@ -71872,7 +71872,7 @@
         <v>466</v>
       </c>
       <c r="D716">
-        <v>64.15000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E716">
         <v>147718</v>
@@ -71913,7 +71913,7 @@
         <v>466</v>
       </c>
       <c r="D717">
-        <v>43.28</v>
+        <v>45.89</v>
       </c>
       <c r="E717">
         <v>217602</v>
@@ -72118,7 +72118,7 @@
         <v>467</v>
       </c>
       <c r="D722">
-        <v>41.11</v>
+        <v>39.98</v>
       </c>
       <c r="E722">
         <v>0</v>
@@ -72200,7 +72200,7 @@
         <v>466</v>
       </c>
       <c r="D724">
-        <v>102.19</v>
+        <v>111.97</v>
       </c>
       <c r="E724">
         <v>89182</v>
@@ -72241,7 +72241,7 @@
         <v>466</v>
       </c>
       <c r="D725">
-        <v>140.49</v>
+        <v>148.35</v>
       </c>
       <c r="E725">
         <v>67312</v>
@@ -72446,7 +72446,7 @@
         <v>467</v>
       </c>
       <c r="D730">
-        <v>148.21</v>
+        <v>151.15</v>
       </c>
       <c r="E730">
         <v>0</v>
@@ -72487,7 +72487,7 @@
         <v>466</v>
       </c>
       <c r="D731">
-        <v>148.21</v>
+        <v>151.15</v>
       </c>
       <c r="E731">
         <v>66065</v>
@@ -72610,7 +72610,7 @@
         <v>467</v>
       </c>
       <c r="D734">
-        <v>120.84</v>
+        <v>126.98</v>
       </c>
       <c r="E734">
         <v>0</v>
@@ -72651,7 +72651,7 @@
         <v>466</v>
       </c>
       <c r="D735">
-        <v>147.75</v>
+        <v>145.39</v>
       </c>
       <c r="E735">
         <v>68682</v>
@@ -72774,7 +72774,7 @@
         <v>467</v>
       </c>
       <c r="D738">
-        <v>220.44</v>
+        <v>219.05</v>
       </c>
       <c r="E738">
         <v>0</v>
@@ -72815,7 +72815,7 @@
         <v>467</v>
       </c>
       <c r="D739">
-        <v>133.59</v>
+        <v>127.45</v>
       </c>
       <c r="E739">
         <v>0</v>
@@ -72856,7 +72856,7 @@
         <v>467</v>
       </c>
       <c r="D740">
-        <v>175.12</v>
+        <v>168.27</v>
       </c>
       <c r="E740">
         <v>0</v>
@@ -72897,7 +72897,7 @@
         <v>466</v>
       </c>
       <c r="D741">
-        <v>136.47</v>
+        <v>147.72</v>
       </c>
       <c r="E741">
         <v>67599</v>
@@ -72938,7 +72938,7 @@
         <v>466</v>
       </c>
       <c r="D742">
-        <v>107.63</v>
+        <v>118.01</v>
       </c>
       <c r="E742">
         <v>84618</v>
@@ -72979,7 +72979,7 @@
         <v>466</v>
       </c>
       <c r="D743">
-        <v>378.75</v>
+        <v>416.62</v>
       </c>
       <c r="E743">
         <v>23968</v>
@@ -73020,7 +73020,7 @@
         <v>467</v>
       </c>
       <c r="D744">
-        <v>107.16</v>
+        <v>108.57</v>
       </c>
       <c r="E744">
         <v>0</v>
@@ -73061,7 +73061,7 @@
         <v>467</v>
       </c>
       <c r="D745">
-        <v>130.6</v>
+        <v>137.94</v>
       </c>
       <c r="E745">
         <v>0</v>
@@ -73102,7 +73102,7 @@
         <v>466</v>
       </c>
       <c r="D746">
-        <v>143.32</v>
+        <v>155.06</v>
       </c>
       <c r="E746">
         <v>64399</v>
@@ -73143,7 +73143,7 @@
         <v>466</v>
       </c>
       <c r="D747">
-        <v>220.9</v>
+        <v>227.83</v>
       </c>
       <c r="E747">
         <v>43829</v>
@@ -73225,7 +73225,7 @@
         <v>467</v>
       </c>
       <c r="D749">
-        <v>410.47</v>
+        <v>418.51</v>
       </c>
       <c r="E749">
         <v>0</v>
@@ -73266,7 +73266,7 @@
         <v>466</v>
       </c>
       <c r="D750">
-        <v>864.21</v>
+        <v>893.84</v>
       </c>
       <c r="E750">
         <v>11171</v>
@@ -73389,7 +73389,7 @@
         <v>467</v>
       </c>
       <c r="D753">
-        <v>225.52</v>
+        <v>219.98</v>
       </c>
       <c r="E753">
         <v>0</v>
@@ -73430,7 +73430,7 @@
         <v>467</v>
       </c>
       <c r="D754">
-        <v>153.59</v>
+        <v>146.74</v>
       </c>
       <c r="E754">
         <v>0</v>
@@ -73471,7 +73471,7 @@
         <v>466</v>
       </c>
       <c r="D755">
-        <v>153.59</v>
+        <v>153.1</v>
       </c>
       <c r="E755">
         <v>65223</v>
@@ -73512,7 +73512,7 @@
         <v>466</v>
       </c>
       <c r="D756">
-        <v>229.68</v>
+        <v>234.3</v>
       </c>
       <c r="E756">
         <v>42619</v>
@@ -73594,7 +73594,7 @@
         <v>467</v>
       </c>
       <c r="D758">
-        <v>232.92</v>
+        <v>223.67</v>
       </c>
       <c r="E758">
         <v>0</v>
@@ -73635,7 +73635,7 @@
         <v>467</v>
       </c>
       <c r="D759">
-        <v>855.67</v>
+        <v>828.29</v>
       </c>
       <c r="E759">
         <v>0</v>
@@ -73717,7 +73717,7 @@
         <v>466</v>
       </c>
       <c r="D761">
-        <v>125.64</v>
+        <v>120.05</v>
       </c>
       <c r="E761">
         <v>83180</v>
@@ -73799,7 +73799,7 @@
         <v>467</v>
       </c>
       <c r="D763">
-        <v>108.42</v>
+        <v>108.89</v>
       </c>
       <c r="E763">
         <v>0</v>
@@ -73840,7 +73840,7 @@
         <v>467</v>
       </c>
       <c r="D764">
-        <v>154.08</v>
+        <v>138.92</v>
       </c>
       <c r="E764">
         <v>0</v>
@@ -73881,7 +73881,7 @@
         <v>466</v>
       </c>
       <c r="D765">
-        <v>121.45</v>
+        <v>120.52</v>
       </c>
       <c r="E765">
         <v>82855</v>
@@ -74004,7 +74004,7 @@
         <v>467</v>
       </c>
       <c r="D768">
-        <v>384.16</v>
+        <v>392.37</v>
       </c>
       <c r="E768">
         <v>0</v>
@@ -74045,7 +74045,7 @@
         <v>466</v>
       </c>
       <c r="D769">
-        <v>394.3</v>
+        <v>400.57</v>
       </c>
       <c r="E769">
         <v>24928</v>
@@ -74168,7 +74168,7 @@
         <v>467</v>
       </c>
       <c r="D772">
-        <v>425.67</v>
+        <v>429.53</v>
       </c>
       <c r="E772">
         <v>0</v>
@@ -74209,7 +74209,7 @@
         <v>466</v>
       </c>
       <c r="D773">
-        <v>18.1</v>
+        <v>18.25</v>
       </c>
       <c r="E773">
         <v>547165</v>
@@ -74332,7 +74332,7 @@
         <v>467</v>
       </c>
       <c r="D776">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="E776">
         <v>0</v>
@@ -74373,7 +74373,7 @@
         <v>467</v>
       </c>
       <c r="D777">
-        <v>120.98</v>
+        <v>120.05</v>
       </c>
       <c r="E777">
         <v>0</v>
@@ -74414,7 +74414,7 @@
         <v>466</v>
       </c>
       <c r="D778">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="E778">
         <v>5738948</v>
@@ -74455,7 +74455,7 @@
         <v>466</v>
       </c>
       <c r="D779">
-        <v>516.77</v>
+        <v>509.03</v>
       </c>
       <c r="E779">
         <v>19617</v>
@@ -74537,7 +74537,7 @@
         <v>467</v>
       </c>
       <c r="D781">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="E781">
         <v>0</v>
@@ -74578,7 +74578,7 @@
         <v>467</v>
       </c>
       <c r="D782">
-        <v>15.35</v>
+        <v>15.3</v>
       </c>
       <c r="E782">
         <v>0</v>
@@ -74619,7 +74619,7 @@
         <v>466</v>
       </c>
       <c r="D783">
-        <v>2521.06</v>
+        <v>2570.11</v>
       </c>
       <c r="E783">
         <v>3885</v>
@@ -74660,7 +74660,7 @@
         <v>466</v>
       </c>
       <c r="D784">
-        <v>99.76000000000001</v>
+        <v>101.12</v>
       </c>
       <c r="E784">
         <v>98751</v>
@@ -74742,7 +74742,7 @@
         <v>467</v>
       </c>
       <c r="D786">
-        <v>481.45</v>
+        <v>494.51</v>
       </c>
       <c r="E786">
         <v>0</v>
@@ -74783,7 +74783,7 @@
         <v>466</v>
       </c>
       <c r="D787">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="E787">
         <v>5228151</v>
@@ -74906,7 +74906,7 @@
         <v>467</v>
       </c>
       <c r="D790">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="E790">
         <v>0</v>
@@ -74947,7 +74947,7 @@
         <v>467</v>
       </c>
       <c r="D791">
-        <v>100.66</v>
+        <v>96.58</v>
       </c>
       <c r="E791">
         <v>0</v>
@@ -74988,7 +74988,7 @@
         <v>466</v>
       </c>
       <c r="D792">
-        <v>126.92</v>
+        <v>129.37</v>
       </c>
       <c r="E792">
         <v>77187</v>
@@ -75029,7 +75029,7 @@
         <v>466</v>
       </c>
       <c r="D793">
-        <v>18</v>
+        <v>17.85</v>
       </c>
       <c r="E793">
         <v>559426</v>
@@ -75111,7 +75111,7 @@
         <v>467</v>
       </c>
       <c r="D795">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="E795">
         <v>0</v>
@@ -75152,7 +75152,7 @@
         <v>467</v>
       </c>
       <c r="D796">
-        <v>124.47</v>
+        <v>120.55</v>
       </c>
       <c r="E796">
         <v>0</v>
@@ -75193,7 +75193,7 @@
         <v>467</v>
       </c>
       <c r="D797">
-        <v>3168.49</v>
+        <v>3124.35</v>
       </c>
       <c r="E797">
         <v>0</v>
@@ -75234,7 +75234,7 @@
         <v>466</v>
       </c>
       <c r="D798">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="E798">
         <v>3768215</v>
@@ -75275,7 +75275,7 @@
         <v>466</v>
       </c>
       <c r="D799">
-        <v>72</v>
+        <v>70.61</v>
       </c>
       <c r="E799">
         <v>141421</v>
@@ -75316,7 +75316,7 @@
         <v>466</v>
       </c>
       <c r="D800">
-        <v>2435.83</v>
+        <v>2376.78</v>
       </c>
       <c r="E800">
         <v>4201</v>
@@ -75357,7 +75357,7 @@
         <v>467</v>
       </c>
       <c r="D801">
-        <v>71.09999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="E801">
         <v>0</v>
@@ -75398,7 +75398,7 @@
         <v>467</v>
       </c>
       <c r="D802">
-        <v>2347.25</v>
+        <v>2509.64</v>
       </c>
       <c r="E802">
         <v>0</v>
@@ -75439,7 +75439,7 @@
         <v>466</v>
       </c>
       <c r="D803">
-        <v>114.09</v>
+        <v>115.51</v>
       </c>
       <c r="E803">
         <v>86449</v>
@@ -75480,7 +75480,7 @@
         <v>466</v>
       </c>
       <c r="D804">
-        <v>836.16</v>
+        <v>846.04</v>
       </c>
       <c r="E804">
         <v>11802</v>
@@ -75562,7 +75562,7 @@
         <v>467</v>
       </c>
       <c r="D806">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="E806">
         <v>0</v>
@@ -75603,7 +75603,7 @@
         <v>467</v>
       </c>
       <c r="D807">
-        <v>834.36</v>
+        <v>832.5599999999999</v>
       </c>
       <c r="E807">
         <v>0</v>
@@ -75644,7 +75644,7 @@
         <v>466</v>
       </c>
       <c r="D808">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="E808">
         <v>3698433</v>
@@ -75685,7 +75685,7 @@
         <v>466</v>
       </c>
       <c r="D809">
-        <v>47.74</v>
+        <v>47.97</v>
       </c>
       <c r="E809">
         <v>208166</v>
@@ -75767,7 +75767,7 @@
         <v>467</v>
       </c>
       <c r="D811">
-        <v>131.67</v>
+        <v>127.4</v>
       </c>
       <c r="E811">
         <v>0</v>
@@ -75808,7 +75808,7 @@
         <v>467</v>
       </c>
       <c r="D812">
-        <v>50.02</v>
+        <v>48.2</v>
       </c>
       <c r="E812">
         <v>0</v>
@@ -75849,7 +75849,7 @@
         <v>466</v>
       </c>
       <c r="D813">
-        <v>130</v>
+        <v>128.5</v>
       </c>
       <c r="E813">
         <v>77710</v>
@@ -75890,7 +75890,7 @@
         <v>466</v>
       </c>
       <c r="D814">
-        <v>124.07</v>
+        <v>120.74</v>
       </c>
       <c r="E814">
         <v>82704</v>
@@ -76013,7 +76013,7 @@
         <v>466</v>
       </c>
       <c r="D817">
-        <v>125.38</v>
+        <v>126.21</v>
       </c>
       <c r="E817">
         <v>79120</v>
@@ -76136,7 +76136,7 @@
         <v>467</v>
       </c>
       <c r="D820">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="E820">
         <v>0</v>
@@ -76177,7 +76177,7 @@
         <v>467</v>
       </c>
       <c r="D821">
-        <v>118.37</v>
+        <v>124.56</v>
       </c>
       <c r="E821">
         <v>0</v>
@@ -76218,7 +76218,7 @@
         <v>466</v>
       </c>
       <c r="D822">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="E822">
         <v>2580302</v>
@@ -76259,7 +76259,7 @@
         <v>466</v>
       </c>
       <c r="D823">
-        <v>52.29</v>
+        <v>53.88</v>
       </c>
       <c r="E823">
         <v>185333</v>
@@ -76341,7 +76341,7 @@
         <v>467</v>
       </c>
       <c r="D825">
-        <v>3.51</v>
+        <v>3.86</v>
       </c>
       <c r="E825">
         <v>0</v>
@@ -76382,7 +76382,7 @@
         <v>466</v>
       </c>
       <c r="D826">
-        <v>3.86</v>
+        <v>4.18</v>
       </c>
       <c r="E826">
         <v>2388940</v>
@@ -76505,7 +76505,7 @@
         <v>467</v>
       </c>
       <c r="D829">
-        <v>57.52</v>
+        <v>55.7</v>
       </c>
       <c r="E829">
         <v>0</v>
@@ -76546,7 +76546,7 @@
         <v>466</v>
       </c>
       <c r="D830">
-        <v>1154.73</v>
+        <v>1158.85</v>
       </c>
       <c r="E830">
         <v>8616</v>
@@ -76915,7 +76915,7 @@
         <v>467</v>
       </c>
       <c r="D839">
-        <v>8.960000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E839">
         <v>0</v>
@@ -76956,7 +76956,7 @@
         <v>467</v>
       </c>
       <c r="D840">
-        <v>251.5</v>
+        <v>276.5</v>
       </c>
       <c r="E840">
         <v>0</v>
@@ -76997,7 +76997,7 @@
         <v>467</v>
       </c>
       <c r="D841">
-        <v>1323.81</v>
+        <v>1360.93</v>
       </c>
       <c r="E841">
         <v>0</v>
@@ -77038,7 +77038,7 @@
         <v>466</v>
       </c>
       <c r="D842">
-        <v>9.23</v>
+        <v>8.32</v>
       </c>
       <c r="E842">
         <v>1200212</v>
@@ -77079,7 +77079,7 @@
         <v>466</v>
       </c>
       <c r="D843">
-        <v>277</v>
+        <v>283.5</v>
       </c>
       <c r="E843">
         <v>35223</v>
@@ -77120,7 +77120,7 @@
         <v>466</v>
       </c>
       <c r="D844">
-        <v>171.04</v>
+        <v>166.09</v>
       </c>
       <c r="E844">
         <v>60122</v>
@@ -77284,7 +77284,7 @@
         <v>467</v>
       </c>
       <c r="D848">
-        <v>300</v>
+        <v>293.5</v>
       </c>
       <c r="E848">
         <v>0</v>
@@ -77325,7 +77325,7 @@
         <v>467</v>
       </c>
       <c r="D849">
-        <v>11.65</v>
+        <v>11.75</v>
       </c>
       <c r="E849">
         <v>0</v>
@@ -77366,7 +77366,7 @@
         <v>467</v>
       </c>
       <c r="D850">
-        <v>203.66</v>
+        <v>185.37</v>
       </c>
       <c r="E850">
         <v>0</v>
@@ -77407,7 +77407,7 @@
         <v>466</v>
       </c>
       <c r="D851">
-        <v>11.15</v>
+        <v>11.7</v>
       </c>
       <c r="E851">
         <v>853484</v>
@@ -77448,7 +77448,7 @@
         <v>466</v>
       </c>
       <c r="D852">
-        <v>185.37</v>
+        <v>203.66</v>
       </c>
       <c r="E852">
         <v>49031</v>
@@ -77489,7 +77489,7 @@
         <v>466</v>
       </c>
       <c r="D853">
-        <v>262.84</v>
+        <v>258.52</v>
       </c>
       <c r="E853">
         <v>38626</v>
@@ -77530,7 +77530,7 @@
         <v>467</v>
       </c>
       <c r="D854">
-        <v>233.05</v>
+        <v>215.27</v>
       </c>
       <c r="E854">
         <v>0</v>
@@ -77571,7 +77571,7 @@
         <v>466</v>
       </c>
       <c r="D855">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E855">
         <v>38406</v>
@@ -77694,7 +77694,7 @@
         <v>467</v>
       </c>
       <c r="D858">
-        <v>190.32</v>
+        <v>185.87</v>
       </c>
       <c r="E858">
         <v>0</v>
@@ -77858,7 +77858,7 @@
         <v>467</v>
       </c>
       <c r="D862">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E862">
         <v>0</v>
@@ -77899,7 +77899,7 @@
         <v>466</v>
       </c>
       <c r="D863">
-        <v>839.61</v>
+        <v>844.49</v>
       </c>
       <c r="E863">
         <v>11824</v>
@@ -78022,7 +78022,7 @@
         <v>467</v>
       </c>
       <c r="D866">
-        <v>739.05</v>
+        <v>753.6900000000001</v>
       </c>
       <c r="E866">
         <v>0</v>
@@ -78063,7 +78063,7 @@
         <v>467</v>
       </c>
       <c r="D867">
-        <v>188.34</v>
+        <v>184.38</v>
       </c>
       <c r="E867">
         <v>0</v>
@@ -78104,7 +78104,7 @@
         <v>467</v>
       </c>
       <c r="D868">
-        <v>18.04</v>
+        <v>16.24</v>
       </c>
       <c r="E868">
         <v>0</v>
@@ -78145,7 +78145,7 @@
         <v>466</v>
       </c>
       <c r="D869">
-        <v>18.04</v>
+        <v>16.24</v>
       </c>
       <c r="E869">
         <v>614887</v>
@@ -78186,7 +78186,7 @@
         <v>466</v>
       </c>
       <c r="D870">
-        <v>184.38</v>
+        <v>190.81</v>
       </c>
       <c r="E870">
         <v>52333</v>
@@ -78227,7 +78227,7 @@
         <v>466</v>
       </c>
       <c r="D871">
-        <v>722.45</v>
+        <v>780.05</v>
       </c>
       <c r="E871">
         <v>12801</v>
@@ -78268,7 +78268,7 @@
         <v>467</v>
       </c>
       <c r="D872">
-        <v>14.63</v>
+        <v>13.5</v>
       </c>
       <c r="E872">
         <v>0</v>
@@ -78309,7 +78309,7 @@
         <v>467</v>
       </c>
       <c r="D873">
-        <v>173.01</v>
+        <v>172.03</v>
       </c>
       <c r="E873">
         <v>0</v>
@@ -78350,7 +78350,7 @@
         <v>467</v>
       </c>
       <c r="D874">
-        <v>683.4</v>
+        <v>684.38</v>
       </c>
       <c r="E874">
         <v>0</v>
@@ -78391,7 +78391,7 @@
         <v>466</v>
       </c>
       <c r="D875">
-        <v>752.72</v>
+        <v>751.74</v>
       </c>
       <c r="E875">
         <v>13283</v>
@@ -78432,7 +78432,7 @@
         <v>466</v>
       </c>
       <c r="D876">
-        <v>178.95</v>
+        <v>175.49</v>
       </c>
       <c r="E876">
         <v>56902</v>
@@ -78473,7 +78473,7 @@
         <v>466</v>
       </c>
       <c r="D877">
-        <v>12.49</v>
+        <v>11.79</v>
       </c>
       <c r="E877">
         <v>846969</v>
@@ -78514,7 +78514,7 @@
         <v>467</v>
       </c>
       <c r="D878">
-        <v>13.79</v>
+        <v>12.78</v>
       </c>
       <c r="E878">
         <v>0</v>
@@ -78555,7 +78555,7 @@
         <v>467</v>
       </c>
       <c r="D879">
-        <v>166.09</v>
+        <v>182.41</v>
       </c>
       <c r="E879">
         <v>0</v>
@@ -78596,7 +78596,7 @@
         <v>466</v>
       </c>
       <c r="D880">
-        <v>1067.26</v>
+        <v>1013.65</v>
       </c>
       <c r="E880">
         <v>9851</v>
@@ -78637,7 +78637,7 @@
         <v>466</v>
       </c>
       <c r="D881">
-        <v>119.5</v>
+        <v>131</v>
       </c>
       <c r="E881">
         <v>76227</v>
@@ -78719,7 +78719,7 @@
         <v>467</v>
       </c>
       <c r="D883">
-        <v>948.35</v>
+        <v>979.54</v>
       </c>
       <c r="E883">
         <v>0</v>
@@ -78760,7 +78760,7 @@
         <v>466</v>
       </c>
       <c r="D884">
-        <v>159.47</v>
+        <v>161.82</v>
       </c>
       <c r="E884">
         <v>61709</v>
@@ -78883,7 +78883,7 @@
         <v>467</v>
       </c>
       <c r="D887">
-        <v>137</v>
+        <v>150.5</v>
       </c>
       <c r="E887">
         <v>0</v>
@@ -78924,7 +78924,7 @@
         <v>467</v>
       </c>
       <c r="D888">
-        <v>791.77</v>
+        <v>786.89</v>
       </c>
       <c r="E888">
         <v>0</v>
@@ -78965,7 +78965,7 @@
         <v>466</v>
       </c>
       <c r="D889">
-        <v>243.24</v>
+        <v>253.43</v>
       </c>
       <c r="E889">
         <v>39402</v>
@@ -79006,7 +79006,7 @@
         <v>466</v>
       </c>
       <c r="D890">
-        <v>97.18000000000001</v>
+        <v>106.57</v>
       </c>
       <c r="E890">
         <v>93701</v>
@@ -79088,7 +79088,7 @@
         <v>467</v>
       </c>
       <c r="D892">
-        <v>105.17</v>
+        <v>102.82</v>
       </c>
       <c r="E892">
         <v>0</v>
@@ -79129,7 +79129,7 @@
         <v>466</v>
       </c>
       <c r="D893">
-        <v>81.03</v>
+        <v>82.83</v>
       </c>
       <c r="E893">
         <v>120557</v>
@@ -79293,7 +79293,7 @@
         <v>466</v>
       </c>
       <c r="D897">
-        <v>27.35</v>
+        <v>29.25</v>
       </c>
       <c r="E897">
         <v>341393</v>
@@ -79416,7 +79416,7 @@
         <v>467</v>
       </c>
       <c r="D900">
-        <v>78.56999999999999</v>
+        <v>81.36</v>
       </c>
       <c r="E900">
         <v>0</v>
@@ -79457,7 +79457,7 @@
         <v>467</v>
       </c>
       <c r="D901">
-        <v>26.45</v>
+        <v>25.8</v>
       </c>
       <c r="E901">
         <v>0</v>
@@ -79498,7 +79498,7 @@
         <v>466</v>
       </c>
       <c r="D902">
-        <v>85.90000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="E902">
         <v>116642</v>
@@ -79539,7 +79539,7 @@
         <v>466</v>
       </c>
       <c r="D903">
-        <v>503.84</v>
+        <v>509.67</v>
       </c>
       <c r="E903">
         <v>19592</v>
@@ -79785,7 +79785,7 @@
         <v>466</v>
       </c>
       <c r="D909">
-        <v>371.5</v>
+        <v>366.72</v>
       </c>
       <c r="E909">
         <v>27229</v>
@@ -79908,7 +79908,7 @@
         <v>467</v>
       </c>
       <c r="D912">
-        <v>80.69</v>
+        <v>75.19</v>
       </c>
       <c r="E912">
         <v>0</v>
@@ -79949,7 +79949,7 @@
         <v>467</v>
       </c>
       <c r="D913">
-        <v>384.41</v>
+        <v>369.11</v>
       </c>
       <c r="E913">
         <v>0</v>
@@ -79990,7 +79990,7 @@
         <v>467</v>
       </c>
       <c r="D914">
-        <v>290.82</v>
+        <v>282.56</v>
       </c>
       <c r="E914">
         <v>0</v>
@@ -80031,7 +80031,7 @@
         <v>466</v>
       </c>
       <c r="D915">
-        <v>228.32</v>
+        <v>212.12</v>
       </c>
       <c r="E915">
         <v>47076</v>
@@ -80072,7 +80072,7 @@
         <v>466</v>
       </c>
       <c r="D916">
-        <v>162.22</v>
+        <v>156.32</v>
       </c>
       <c r="E916">
         <v>63880</v>
@@ -80113,7 +80113,7 @@
         <v>466</v>
       </c>
       <c r="D917">
-        <v>194.5</v>
+        <v>178.5</v>
       </c>
       <c r="E917">
         <v>55942</v>
@@ -80154,7 +80154,7 @@
         <v>467</v>
       </c>
       <c r="D918">
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="E918">
         <v>0</v>
@@ -80195,7 +80195,7 @@
         <v>466</v>
       </c>
       <c r="D919">
-        <v>374.85</v>
+        <v>371.02</v>
       </c>
       <c r="E919">
         <v>26914</v>
@@ -80318,7 +80318,7 @@
         <v>467</v>
       </c>
       <c r="D922">
-        <v>155.34</v>
+        <v>161.24</v>
       </c>
       <c r="E922">
         <v>0</v>
@@ -80359,7 +80359,7 @@
         <v>467</v>
       </c>
       <c r="D923">
-        <v>197.88</v>
+        <v>199.35</v>
       </c>
       <c r="E923">
         <v>0</v>
@@ -80400,7 +80400,7 @@
         <v>466</v>
       </c>
       <c r="D924">
-        <v>230.28</v>
+        <v>245.5</v>
       </c>
       <c r="E924">
         <v>40675</v>
@@ -80441,7 +80441,7 @@
         <v>466</v>
       </c>
       <c r="D925">
-        <v>1527.42</v>
+        <v>1468.29</v>
       </c>
       <c r="E925">
         <v>6800</v>
@@ -80523,7 +80523,7 @@
         <v>467</v>
       </c>
       <c r="D927">
-        <v>220.95</v>
+        <v>198.86</v>
       </c>
       <c r="E927">
         <v>0</v>
@@ -80564,7 +80564,7 @@
         <v>467</v>
       </c>
       <c r="D928">
-        <v>338.53</v>
+        <v>348.31</v>
       </c>
       <c r="E928">
         <v>0</v>
@@ -80605,7 +80605,7 @@
         <v>467</v>
       </c>
       <c r="D929">
-        <v>1517.56</v>
+        <v>1665.38</v>
       </c>
       <c r="E929">
         <v>0</v>
@@ -80646,7 +80646,7 @@
         <v>466</v>
       </c>
       <c r="D930">
-        <v>202.3</v>
+        <v>204.26</v>
       </c>
       <c r="E930">
         <v>48887</v>
@@ -80687,7 +80687,7 @@
         <v>466</v>
       </c>
       <c r="D931">
-        <v>707.95</v>
+        <v>759.0599999999999</v>
       </c>
       <c r="E931">
         <v>13155</v>
@@ -80728,7 +80728,7 @@
         <v>466</v>
       </c>
       <c r="D932">
-        <v>359.08</v>
+        <v>375.22</v>
       </c>
       <c r="E932">
         <v>26613</v>
@@ -80769,7 +80769,7 @@
         <v>467</v>
       </c>
       <c r="D933">
-        <v>395.77</v>
+        <v>411.42</v>
       </c>
       <c r="E933">
         <v>0</v>
@@ -80810,7 +80810,7 @@
         <v>466</v>
       </c>
       <c r="D934">
-        <v>1941.3</v>
+        <v>1931.44</v>
       </c>
       <c r="E934">
         <v>5170</v>
@@ -80933,7 +80933,7 @@
         <v>467</v>
       </c>
       <c r="D937">
-        <v>1882.17</v>
+        <v>2020.13</v>
       </c>
       <c r="E937">
         <v>0</v>
@@ -80974,7 +80974,7 @@
         <v>467</v>
       </c>
       <c r="D938">
-        <v>807.29</v>
+        <v>790.89</v>
       </c>
       <c r="E938">
         <v>0</v>
@@ -81015,7 +81015,7 @@
         <v>466</v>
       </c>
       <c r="D939">
-        <v>786</v>
+        <v>801.76</v>
       </c>
       <c r="E939">
         <v>12454</v>
@@ -81056,7 +81056,7 @@
         <v>466</v>
       </c>
       <c r="D940">
-        <v>422.18</v>
+        <v>459.36</v>
       </c>
       <c r="E940">
         <v>21738</v>
@@ -81138,7 +81138,7 @@
         <v>467</v>
       </c>
       <c r="D942">
-        <v>423.65</v>
+        <v>407.02</v>
       </c>
       <c r="E942">
         <v>0</v>
@@ -81179,7 +81179,7 @@
         <v>467</v>
       </c>
       <c r="D943">
-        <v>247.96</v>
+        <v>242.56</v>
       </c>
       <c r="E943">
         <v>0</v>
@@ -81220,7 +81220,7 @@
         <v>466</v>
       </c>
       <c r="D944">
-        <v>498.46</v>
+        <v>496.55</v>
       </c>
       <c r="E944">
         <v>20110</v>
@@ -81261,7 +81261,7 @@
         <v>466</v>
       </c>
       <c r="D945">
-        <v>247.96</v>
+        <v>242.56</v>
       </c>
       <c r="E945">
         <v>41168</v>
@@ -81343,7 +81343,7 @@
         <v>467</v>
       </c>
       <c r="D947">
-        <v>721.98</v>
+        <v>732.8200000000001</v>
       </c>
       <c r="E947">
         <v>0</v>
@@ -81384,7 +81384,7 @@
         <v>467</v>
       </c>
       <c r="D948">
-        <v>223.9</v>
+        <v>236.67</v>
       </c>
       <c r="E948">
         <v>0</v>
@@ -81425,7 +81425,7 @@
         <v>467</v>
       </c>
       <c r="D949">
-        <v>447.37</v>
+        <v>451.19</v>
       </c>
       <c r="E949">
         <v>0</v>
@@ -81466,7 +81466,7 @@
         <v>466</v>
       </c>
       <c r="D950">
-        <v>378.91</v>
+        <v>395.01</v>
       </c>
       <c r="E950">
         <v>25279</v>
@@ -81507,7 +81507,7 @@
         <v>466</v>
       </c>
       <c r="D951">
-        <v>1719.58</v>
+        <v>1887.1</v>
       </c>
       <c r="E951">
         <v>5291</v>
@@ -81548,7 +81548,7 @@
         <v>466</v>
       </c>
       <c r="D952">
-        <v>738.73</v>
+        <v>768.27</v>
       </c>
       <c r="E952">
         <v>12997</v>
@@ -81589,7 +81589,7 @@
         <v>467</v>
       </c>
       <c r="D953">
-        <v>1911.73</v>
+        <v>1793.48</v>
       </c>
       <c r="E953">
         <v>0</v>
@@ -81630,7 +81630,7 @@
         <v>466</v>
       </c>
       <c r="D954">
-        <v>247.06</v>
+        <v>250.88</v>
       </c>
       <c r="E954">
         <v>39802</v>
@@ -81753,7 +81753,7 @@
         <v>467</v>
       </c>
       <c r="D957">
-        <v>735.77</v>
+        <v>752.52</v>
       </c>
       <c r="E957">
         <v>0</v>
@@ -81794,7 +81794,7 @@
         <v>466</v>
       </c>
       <c r="D958">
-        <v>295.07</v>
+        <v>324.53</v>
       </c>
       <c r="E958">
         <v>30769</v>
@@ -81917,7 +81917,7 @@
         <v>467</v>
       </c>
       <c r="D961">
-        <v>236.57</v>
+        <v>250.88</v>
       </c>
       <c r="E961">
         <v>0</v>
@@ -81958,7 +81958,7 @@
         <v>467</v>
       </c>
       <c r="D962">
-        <v>481.81</v>
+        <v>477.91</v>
       </c>
       <c r="E962">
         <v>0</v>
@@ -81999,7 +81999,7 @@
         <v>466</v>
       </c>
       <c r="D963">
-        <v>477.91</v>
+        <v>465.72</v>
       </c>
       <c r="E963">
         <v>21441</v>
@@ -82040,7 +82040,7 @@
         <v>466</v>
       </c>
       <c r="D964">
-        <v>258.99</v>
+        <v>251.83</v>
       </c>
       <c r="E964">
         <v>39652</v>
@@ -82122,7 +82122,7 @@
         <v>467</v>
       </c>
       <c r="D966">
-        <v>341.5</v>
+        <v>338.51</v>
       </c>
       <c r="E966">
         <v>0</v>
@@ -82163,7 +82163,7 @@
         <v>466</v>
       </c>
       <c r="D967">
-        <v>339.01</v>
+        <v>351.99</v>
       </c>
       <c r="E967">
         <v>28369</v>
@@ -82286,7 +82286,7 @@
         <v>467</v>
       </c>
       <c r="D970">
-        <v>426.71</v>
+        <v>434.51</v>
       </c>
       <c r="E970">
         <v>0</v>
@@ -82327,7 +82327,7 @@
         <v>467</v>
       </c>
       <c r="D971">
-        <v>323.53</v>
+        <v>330.02</v>
       </c>
       <c r="E971">
         <v>0</v>
@@ -82368,7 +82368,7 @@
         <v>467</v>
       </c>
       <c r="D972">
-        <v>222.26</v>
+        <v>232.76</v>
       </c>
       <c r="E972">
         <v>0</v>
@@ -82409,7 +82409,7 @@
         <v>466</v>
       </c>
       <c r="D973">
-        <v>330.02</v>
+        <v>322.03</v>
       </c>
       <c r="E973">
         <v>31008</v>
@@ -82450,7 +82450,7 @@
         <v>466</v>
       </c>
       <c r="D974">
-        <v>438.9</v>
+        <v>443.29</v>
       </c>
       <c r="E974">
         <v>22526</v>
@@ -82491,7 +82491,7 @@
         <v>466</v>
       </c>
       <c r="D975">
-        <v>139.83</v>
+        <v>138.34</v>
       </c>
       <c r="E975">
         <v>72182</v>
@@ -82532,7 +82532,7 @@
         <v>467</v>
       </c>
       <c r="D976">
-        <v>453.04</v>
+        <v>455.97</v>
       </c>
       <c r="E976">
         <v>0</v>
@@ -82573,7 +82573,7 @@
         <v>466</v>
       </c>
       <c r="D977">
-        <v>444.66</v>
+        <v>431.01</v>
       </c>
       <c r="E977">
         <v>23168</v>
@@ -82696,7 +82696,7 @@
         <v>467</v>
       </c>
       <c r="D980">
-        <v>337.01</v>
+        <v>333.02</v>
       </c>
       <c r="E980">
         <v>0</v>
@@ -82737,7 +82737,7 @@
         <v>467</v>
       </c>
       <c r="D981">
-        <v>144.78</v>
+        <v>139.83</v>
       </c>
       <c r="E981">
         <v>0</v>
@@ -82778,7 +82778,7 @@
         <v>467</v>
       </c>
       <c r="D982">
-        <v>410.53</v>
+        <v>386.15</v>
       </c>
       <c r="E982">
         <v>0</v>
@@ -82819,7 +82819,7 @@
         <v>466</v>
       </c>
       <c r="D983">
-        <v>337.51</v>
+        <v>304.06</v>
       </c>
       <c r="E983">
         <v>32841</v>
@@ -82860,7 +82860,7 @@
         <v>466</v>
       </c>
       <c r="D984">
-        <v>14.29</v>
+        <v>14.27</v>
       </c>
       <c r="E984">
         <v>699773</v>
@@ -82901,7 +82901,7 @@
         <v>466</v>
       </c>
       <c r="D985">
-        <v>716.25</v>
+        <v>708.33</v>
       </c>
       <c r="E985">
         <v>14097</v>
@@ -82942,7 +82942,7 @@
         <v>467</v>
       </c>
       <c r="D986">
-        <v>751.92</v>
+        <v>699.41</v>
       </c>
       <c r="E986">
         <v>0</v>
@@ -82983,7 +82983,7 @@
         <v>466</v>
       </c>
       <c r="D987">
-        <v>164.16</v>
+        <v>167.9</v>
       </c>
       <c r="E987">
         <v>59474</v>
@@ -83106,7 +83106,7 @@
         <v>467</v>
       </c>
       <c r="D990">
-        <v>333.52</v>
+        <v>321.53</v>
       </c>
       <c r="E990">
         <v>0</v>
@@ -83147,7 +83147,7 @@
         <v>466</v>
       </c>
       <c r="D991">
-        <v>354.49</v>
+        <v>368.96</v>
       </c>
       <c r="E991">
         <v>27064</v>
@@ -83270,7 +83270,7 @@
         <v>467</v>
       </c>
       <c r="D994">
-        <v>191.29</v>
+        <v>189.42</v>
       </c>
       <c r="E994">
         <v>0</v>
@@ -83311,7 +83311,7 @@
         <v>467</v>
       </c>
       <c r="D995">
-        <v>353.49</v>
+        <v>365.47</v>
       </c>
       <c r="E995">
         <v>0</v>
@@ -83352,7 +83352,7 @@
         <v>466</v>
       </c>
       <c r="D996">
-        <v>188.02</v>
+        <v>180.06</v>
       </c>
       <c r="E996">
         <v>55458</v>
@@ -83393,7 +83393,7 @@
         <v>466</v>
       </c>
       <c r="D997">
-        <v>877.73</v>
+        <v>861.88</v>
       </c>
       <c r="E997">
         <v>11586</v>
@@ -83475,7 +83475,7 @@
         <v>467</v>
       </c>
       <c r="D999">
-        <v>23.15</v>
+        <v>23.67</v>
       </c>
       <c r="E999">
         <v>0</v>
@@ -83516,7 +83516,7 @@
         <v>467</v>
       </c>
       <c r="D1000">
-        <v>839.1</v>
+        <v>806.41</v>
       </c>
       <c r="E1000">
         <v>0</v>
@@ -83557,7 +83557,7 @@
         <v>466</v>
       </c>
       <c r="D1001">
-        <v>23.67</v>
+        <v>24.22</v>
       </c>
       <c r="E1001">
         <v>412294</v>
@@ -83598,7 +83598,7 @@
         <v>466</v>
       </c>
       <c r="D1002">
-        <v>3313.83</v>
+        <v>3204.86</v>
       </c>
       <c r="E1002">
         <v>3115</v>
@@ -83803,7 +83803,7 @@
         <v>467</v>
       </c>
       <c r="D1007">
-        <v>36.77</v>
+        <v>36.57</v>
       </c>
       <c r="E1007">
         <v>0</v>
@@ -83844,7 +83844,7 @@
         <v>467</v>
       </c>
       <c r="D1008">
-        <v>2967.09</v>
+        <v>3066.16</v>
       </c>
       <c r="E1008">
         <v>0</v>
@@ -83885,7 +83885,7 @@
         <v>466</v>
       </c>
       <c r="D1009">
-        <v>37.17</v>
+        <v>38.92</v>
       </c>
       <c r="E1009">
         <v>256571</v>
@@ -83926,7 +83926,7 @@
         <v>466</v>
       </c>
       <c r="D1010">
-        <v>3170.18</v>
+        <v>3046.35</v>
       </c>
       <c r="E1010">
         <v>3277</v>
@@ -84008,7 +84008,7 @@
         <v>467</v>
       </c>
       <c r="D1012">
-        <v>179.6</v>
+        <v>177.26</v>
       </c>
       <c r="E1012">
         <v>0</v>
@@ -84049,7 +84049,7 @@
         <v>467</v>
       </c>
       <c r="D1013">
-        <v>2768.96</v>
+        <v>2818.49</v>
       </c>
       <c r="E1013">
         <v>0</v>
@@ -84090,7 +84090,7 @@
         <v>466</v>
       </c>
       <c r="D1014">
-        <v>171.18</v>
+        <v>174.45</v>
       </c>
       <c r="E1014">
         <v>57241</v>
@@ -84213,7 +84213,7 @@
         <v>467</v>
       </c>
       <c r="D1017">
-        <v>40.81</v>
+        <v>36.77</v>
       </c>
       <c r="E1017">
         <v>0</v>
@@ -84254,7 +84254,7 @@
         <v>467</v>
       </c>
       <c r="D1018">
-        <v>172.58</v>
+        <v>155.74</v>
       </c>
       <c r="E1018">
         <v>0</v>
@@ -84295,7 +84295,7 @@
         <v>467</v>
       </c>
       <c r="D1019">
-        <v>2922.51</v>
+        <v>3214.76</v>
       </c>
       <c r="E1019">
         <v>0</v>
@@ -84336,7 +84336,7 @@
         <v>466</v>
       </c>
       <c r="D1020">
-        <v>41.01</v>
+        <v>42.91</v>
       </c>
       <c r="E1020">
         <v>232714</v>
@@ -84377,7 +84377,7 @@
         <v>466</v>
       </c>
       <c r="D1021">
-        <v>172.58</v>
+        <v>155.74</v>
       </c>
       <c r="E1021">
         <v>64118</v>
@@ -84418,7 +84418,7 @@
         <v>466</v>
       </c>
       <c r="D1022">
-        <v>230.07</v>
+        <v>221.64</v>
       </c>
       <c r="E1022">
         <v>45054</v>
@@ -84459,7 +84459,7 @@
         <v>467</v>
       </c>
       <c r="D1023">
-        <v>40.31</v>
+        <v>39.41</v>
       </c>
       <c r="E1023">
         <v>0</v>
@@ -84500,7 +84500,7 @@
         <v>467</v>
       </c>
       <c r="D1024">
-        <v>173.52</v>
+        <v>171.18</v>
       </c>
       <c r="E1024">
         <v>0</v>
@@ -84541,7 +84541,7 @@
         <v>467</v>
       </c>
       <c r="D1025">
-        <v>244.94</v>
+        <v>220.65</v>
       </c>
       <c r="E1025">
         <v>0</v>
@@ -84582,7 +84582,7 @@
         <v>466</v>
       </c>
       <c r="D1026">
-        <v>39.41</v>
+        <v>39.91</v>
       </c>
       <c r="E1026">
         <v>250207</v>
@@ -84623,7 +84623,7 @@
         <v>466</v>
       </c>
       <c r="D1027">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E1027">
         <v>112706</v>
@@ -84664,7 +84664,7 @@
         <v>466</v>
       </c>
       <c r="D1028">
-        <v>357</v>
+        <v>342.5</v>
       </c>
       <c r="E1028">
         <v>29155</v>
@@ -84828,7 +84828,7 @@
         <v>467</v>
       </c>
       <c r="D1032">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="E1032">
         <v>0</v>
@@ -84869,7 +84869,7 @@
         <v>467</v>
       </c>
       <c r="D1033">
-        <v>39.41</v>
+        <v>39.91</v>
       </c>
       <c r="E1033">
         <v>0</v>
@@ -84910,7 +84910,7 @@
         <v>466</v>
       </c>
       <c r="D1034">
-        <v>39.41</v>
+        <v>39.91</v>
       </c>
       <c r="E1034">
         <v>250207</v>
@@ -84951,7 +84951,7 @@
         <v>466</v>
       </c>
       <c r="D1035">
-        <v>246.29</v>
+        <v>240.34</v>
       </c>
       <c r="E1035">
         <v>41548</v>
@@ -85033,7 +85033,7 @@
         <v>467</v>
       </c>
       <c r="D1037">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1037">
         <v>0</v>
@@ -85074,7 +85074,7 @@
         <v>466</v>
       </c>
       <c r="D1038">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1038">
         <v>114778</v>
@@ -85197,7 +85197,7 @@
         <v>467</v>
       </c>
       <c r="D1041">
-        <v>228.94</v>
+        <v>229.93</v>
       </c>
       <c r="E1041">
         <v>0</v>
@@ -85238,7 +85238,7 @@
         <v>466</v>
       </c>
       <c r="D1042">
-        <v>451.71</v>
+        <v>449.25</v>
       </c>
       <c r="E1042">
         <v>22227</v>
@@ -85361,7 +85361,7 @@
         <v>467</v>
       </c>
       <c r="D1045">
-        <v>433.05</v>
+        <v>434.03</v>
       </c>
       <c r="E1045">
         <v>0</v>
@@ -85402,7 +85402,7 @@
         <v>467</v>
       </c>
       <c r="D1046">
-        <v>89.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="E1046">
         <v>0</v>
@@ -85443,7 +85443,7 @@
         <v>466</v>
       </c>
       <c r="D1047">
-        <v>193.77</v>
+        <v>183.86</v>
       </c>
       <c r="E1047">
         <v>54311</v>
@@ -85484,7 +85484,7 @@
         <v>466</v>
       </c>
       <c r="D1048">
-        <v>201.54</v>
+        <v>197.61</v>
       </c>
       <c r="E1048">
         <v>50532</v>
@@ -85566,7 +85566,7 @@
         <v>467</v>
       </c>
       <c r="D1050">
-        <v>169.59</v>
+        <v>168.61</v>
       </c>
       <c r="E1050">
         <v>0</v>
@@ -85607,7 +85607,7 @@
         <v>467</v>
       </c>
       <c r="D1051">
-        <v>71.34999999999999</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="E1051">
         <v>0</v>
@@ -85648,7 +85648,7 @@
         <v>467</v>
       </c>
       <c r="D1052">
-        <v>169.49</v>
+        <v>152.64</v>
       </c>
       <c r="E1052">
         <v>0</v>
@@ -85689,7 +85689,7 @@
         <v>466</v>
       </c>
       <c r="D1053">
-        <v>64.26000000000001</v>
+        <v>57.87</v>
       </c>
       <c r="E1053">
         <v>172555</v>
@@ -85730,7 +85730,7 @@
         <v>466</v>
       </c>
       <c r="D1054">
-        <v>169.49</v>
+        <v>152.64</v>
       </c>
       <c r="E1054">
         <v>65420</v>
@@ -85771,7 +85771,7 @@
         <v>466</v>
       </c>
       <c r="D1055">
-        <v>37</v>
+        <v>33.55</v>
       </c>
       <c r="E1055">
         <v>297638</v>
@@ -85812,7 +85812,7 @@
         <v>467</v>
       </c>
       <c r="D1056">
-        <v>52.09</v>
+        <v>57.28</v>
       </c>
       <c r="E1056">
         <v>0</v>
@@ -85853,7 +85853,7 @@
         <v>467</v>
       </c>
       <c r="D1057">
-        <v>30.2</v>
+        <v>33.2</v>
       </c>
       <c r="E1057">
         <v>0</v>
@@ -85894,7 +85894,7 @@
         <v>467</v>
       </c>
       <c r="D1058">
-        <v>137.77</v>
+        <v>151.15</v>
       </c>
       <c r="E1058">
         <v>0</v>
@@ -85935,7 +85935,7 @@
         <v>466</v>
       </c>
       <c r="D1059">
-        <v>66.36</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E1059">
         <v>152547</v>
@@ -85976,7 +85976,7 @@
         <v>466</v>
       </c>
       <c r="D1060">
-        <v>150.65</v>
+        <v>135.79</v>
       </c>
       <c r="E1060">
         <v>73538</v>
@@ -86017,7 +86017,7 @@
         <v>466</v>
       </c>
       <c r="D1061">
-        <v>131.48</v>
+        <v>131.94</v>
       </c>
       <c r="E1061">
         <v>75684</v>
@@ -86058,7 +86058,7 @@
         <v>467</v>
       </c>
       <c r="D1062">
-        <v>57.28</v>
+        <v>51.59</v>
       </c>
       <c r="E1062">
         <v>0</v>
@@ -86099,7 +86099,7 @@
         <v>467</v>
       </c>
       <c r="D1063">
-        <v>119.43</v>
+        <v>117.95</v>
       </c>
       <c r="E1063">
         <v>0</v>
@@ -86140,7 +86140,7 @@
         <v>466</v>
       </c>
       <c r="D1064">
-        <v>38.6</v>
+        <v>37.4</v>
       </c>
       <c r="E1064">
         <v>266999</v>
@@ -86181,7 +86181,7 @@
         <v>466</v>
       </c>
       <c r="D1065">
-        <v>50.49</v>
+        <v>55.48</v>
       </c>
       <c r="E1065">
         <v>179988</v>
@@ -86263,7 +86263,7 @@
         <v>467</v>
       </c>
       <c r="D1067">
-        <v>137.5</v>
+        <v>129.17</v>
       </c>
       <c r="E1067">
         <v>0</v>
@@ -86427,7 +86427,7 @@
         <v>467</v>
       </c>
       <c r="D1071">
-        <v>59.97</v>
+        <v>60.97</v>
       </c>
       <c r="E1071">
         <v>0</v>
@@ -86468,7 +86468,7 @@
         <v>467</v>
       </c>
       <c r="D1072">
-        <v>37.2</v>
+        <v>40.9</v>
       </c>
       <c r="E1072">
         <v>0</v>
@@ -86509,7 +86509,7 @@
         <v>466</v>
       </c>
       <c r="D1073">
-        <v>64.76000000000001</v>
+        <v>64.86</v>
       </c>
       <c r="E1073">
         <v>153958</v>
@@ -86550,7 +86550,7 @@
         <v>466</v>
       </c>
       <c r="D1074">
-        <v>666.26</v>
+        <v>665.27</v>
       </c>
       <c r="E1074">
         <v>15010</v>
@@ -86632,7 +86632,7 @@
         <v>467</v>
       </c>
       <c r="D1076">
-        <v>667.24</v>
+        <v>710.67</v>
       </c>
       <c r="E1076">
         <v>0</v>
@@ -86673,7 +86673,7 @@
         <v>466</v>
       </c>
       <c r="D1077">
-        <v>107.97</v>
+        <v>110.86</v>
       </c>
       <c r="E1077">
         <v>90075</v>
@@ -86796,7 +86796,7 @@
         <v>467</v>
       </c>
       <c r="D1080">
-        <v>57.67</v>
+        <v>58.07</v>
       </c>
       <c r="E1080">
         <v>0</v>
@@ -86837,7 +86837,7 @@
         <v>467</v>
       </c>
       <c r="D1081">
-        <v>108.45</v>
+        <v>104.12</v>
       </c>
       <c r="E1081">
         <v>0</v>
@@ -86878,7 +86878,7 @@
         <v>467</v>
       </c>
       <c r="D1082">
-        <v>175.43</v>
+        <v>177.42</v>
       </c>
       <c r="E1082">
         <v>0</v>
@@ -86919,7 +86919,7 @@
         <v>466</v>
       </c>
       <c r="D1083">
-        <v>108.45</v>
+        <v>104.12</v>
       </c>
       <c r="E1083">
         <v>95906</v>
@@ -86960,7 +86960,7 @@
         <v>466</v>
       </c>
       <c r="D1084">
-        <v>711.66</v>
+        <v>739.3</v>
       </c>
       <c r="E1084">
         <v>13507</v>
@@ -87001,7 +87001,7 @@
         <v>466</v>
       </c>
       <c r="D1085">
-        <v>869.8099999999999</v>
+        <v>881.7</v>
       </c>
       <c r="E1085">
         <v>11325</v>
@@ -87042,7 +87042,7 @@
         <v>467</v>
       </c>
       <c r="D1086">
-        <v>97.84999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="E1086">
         <v>0</v>
@@ -87083,7 +87083,7 @@
         <v>467</v>
       </c>
       <c r="D1087">
-        <v>833.15</v>
+        <v>861.88</v>
       </c>
       <c r="E1087">
         <v>0</v>
@@ -87124,7 +87124,7 @@
         <v>466</v>
       </c>
       <c r="D1088">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="E1088">
         <v>193148</v>
@@ -87247,7 +87247,7 @@
         <v>467</v>
       </c>
       <c r="D1091">
-        <v>52.9</v>
+        <v>53.8</v>
       </c>
       <c r="E1091">
         <v>0</v>
@@ -87288,7 +87288,7 @@
         <v>467</v>
       </c>
       <c r="D1092">
-        <v>2451.73</v>
+        <v>2476</v>
       </c>
       <c r="E1092">
         <v>0</v>
@@ -87329,7 +87329,7 @@
         <v>466</v>
       </c>
       <c r="D1093">
-        <v>1556.98</v>
+        <v>1502.78</v>
       </c>
       <c r="E1093">
         <v>6644</v>
@@ -87370,7 +87370,7 @@
         <v>466</v>
       </c>
       <c r="D1094">
-        <v>743.49</v>
+        <v>750.4299999999999</v>
       </c>
       <c r="E1094">
         <v>13306</v>
@@ -87452,7 +87452,7 @@
         <v>467</v>
       </c>
       <c r="D1096">
-        <v>730.6</v>
+        <v>738.53</v>
       </c>
       <c r="E1096">
         <v>0</v>
@@ -87493,7 +87493,7 @@
         <v>466</v>
       </c>
       <c r="D1097">
-        <v>126.5</v>
+        <v>122.5</v>
       </c>
       <c r="E1097">
         <v>81516</v>
@@ -87616,7 +87616,7 @@
         <v>467</v>
       </c>
       <c r="D1100">
-        <v>891.3</v>
+        <v>915.98</v>
       </c>
       <c r="E1100">
         <v>0</v>
@@ -87657,7 +87657,7 @@
         <v>466</v>
       </c>
       <c r="D1101">
-        <v>752.41</v>
+        <v>776.2</v>
       </c>
       <c r="E1101">
         <v>12864</v>
@@ -87780,7 +87780,7 @@
         <v>467</v>
       </c>
       <c r="D1104">
-        <v>1566.83</v>
+        <v>1581.62</v>
       </c>
       <c r="E1104">
         <v>0</v>
@@ -87821,7 +87821,7 @@
         <v>467</v>
       </c>
       <c r="D1105">
-        <v>124</v>
+        <v>116.5</v>
       </c>
       <c r="E1105">
         <v>0</v>
@@ -87862,7 +87862,7 @@
         <v>466</v>
       </c>
       <c r="D1106">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E1106">
         <v>39469</v>
@@ -87903,7 +87903,7 @@
         <v>466</v>
       </c>
       <c r="D1107">
-        <v>1561.91</v>
+        <v>1581.62</v>
       </c>
       <c r="E1107">
         <v>6313</v>
@@ -87985,7 +87985,7 @@
         <v>467</v>
       </c>
       <c r="D1109">
-        <v>883.27</v>
+        <v>864.4299999999999</v>
       </c>
       <c r="E1109">
         <v>0</v>
@@ -88149,7 +88149,7 @@
         <v>467</v>
       </c>
       <c r="D1113">
-        <v>263</v>
+        <v>261.5</v>
       </c>
       <c r="E1113">
         <v>0</v>
@@ -88190,7 +88190,7 @@
         <v>467</v>
       </c>
       <c r="D1114">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="E1114">
         <v>0</v>
@@ -88231,7 +88231,7 @@
         <v>466</v>
       </c>
       <c r="D1115">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E1115">
         <v>94205</v>
@@ -88272,7 +88272,7 @@
         <v>466</v>
       </c>
       <c r="D1116">
-        <v>212.22</v>
+        <v>206.26</v>
       </c>
       <c r="E1116">
         <v>48413</v>
@@ -88395,7 +88395,7 @@
         <v>467</v>
       </c>
       <c r="D1119">
-        <v>203.77</v>
+        <v>199.3</v>
       </c>
       <c r="E1119">
         <v>0</v>
@@ -88436,7 +88436,7 @@
         <v>466</v>
       </c>
       <c r="D1120">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1120">
         <v>188410</v>
@@ -88477,7 +88477,7 @@
         <v>466</v>
       </c>
       <c r="D1121">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="E1121">
         <v>16080</v>
@@ -88682,7 +88682,7 @@
         <v>467</v>
       </c>
       <c r="D1126">
-        <v>72.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="E1126">
         <v>0</v>
@@ -88723,7 +88723,7 @@
         <v>467</v>
       </c>
       <c r="D1127">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="E1127">
         <v>0</v>
@@ -88764,7 +88764,7 @@
         <v>467</v>
       </c>
       <c r="D1128">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E1128">
         <v>0</v>
@@ -88805,7 +88805,7 @@
         <v>466</v>
       </c>
       <c r="D1129">
-        <v>178</v>
+        <v>180.5</v>
       </c>
       <c r="E1129">
         <v>55322</v>
@@ -88846,7 +88846,7 @@
         <v>466</v>
       </c>
       <c r="D1130">
-        <v>194.5</v>
+        <v>190</v>
       </c>
       <c r="E1130">
         <v>52556</v>
@@ -88887,7 +88887,7 @@
         <v>466</v>
       </c>
       <c r="D1131">
-        <v>193.48</v>
+        <v>190.71</v>
       </c>
       <c r="E1131">
         <v>52361</v>
@@ -88928,7 +88928,7 @@
         <v>467</v>
       </c>
       <c r="D1132">
-        <v>202</v>
+        <v>210.5</v>
       </c>
       <c r="E1132">
         <v>0</v>
@@ -88969,7 +88969,7 @@
         <v>467</v>
       </c>
       <c r="D1133">
-        <v>211.44</v>
+        <v>210.06</v>
       </c>
       <c r="E1133">
         <v>0</v>
@@ -89010,7 +89010,7 @@
         <v>466</v>
       </c>
       <c r="D1134">
-        <v>885.9</v>
+        <v>974.29</v>
       </c>
       <c r="E1134">
         <v>10249</v>
@@ -89051,7 +89051,7 @@
         <v>466</v>
       </c>
       <c r="D1135">
-        <v>123</v>
+        <v>117.5</v>
       </c>
       <c r="E1135">
         <v>84985</v>
@@ -89133,7 +89133,7 @@
         <v>467</v>
       </c>
       <c r="D1137">
-        <v>196</v>
+        <v>215.5</v>
       </c>
       <c r="E1137">
         <v>0</v>
@@ -89174,7 +89174,7 @@
         <v>467</v>
       </c>
       <c r="D1138">
-        <v>848.16</v>
+        <v>890.86</v>
       </c>
       <c r="E1138">
         <v>0</v>
@@ -89256,7 +89256,7 @@
         <v>466</v>
       </c>
       <c r="D1140">
-        <v>232.5</v>
+        <v>255.5</v>
       </c>
       <c r="E1140">
         <v>39083</v>
@@ -89297,7 +89297,7 @@
         <v>466</v>
       </c>
       <c r="D1141">
-        <v>117.25</v>
+        <v>112.76</v>
       </c>
       <c r="E1141">
         <v>88557</v>
@@ -89338,7 +89338,7 @@
         <v>466</v>
       </c>
       <c r="D1142">
-        <v>955.42</v>
+        <v>978.26</v>
       </c>
       <c r="E1142">
         <v>10207</v>
@@ -89379,7 +89379,7 @@
         <v>467</v>
       </c>
       <c r="D1143">
-        <v>233.5</v>
+        <v>210.5</v>
       </c>
       <c r="E1143">
         <v>0</v>
@@ -89420,7 +89420,7 @@
         <v>467</v>
       </c>
       <c r="D1144">
-        <v>840.21</v>
+        <v>828.29</v>
       </c>
       <c r="E1144">
         <v>0</v>
@@ -89461,7 +89461,7 @@
         <v>466</v>
       </c>
       <c r="D1145">
-        <v>214</v>
+        <v>209.5</v>
       </c>
       <c r="E1145">
         <v>47664</v>
@@ -89502,7 +89502,7 @@
         <v>466</v>
       </c>
       <c r="D1146">
-        <v>828.29</v>
+        <v>773.67</v>
       </c>
       <c r="E1146">
         <v>12907</v>
@@ -89584,7 +89584,7 @@
         <v>467</v>
       </c>
       <c r="D1148">
-        <v>779.63</v>
+        <v>766.72</v>
       </c>
       <c r="E1148">
         <v>0</v>
@@ -89625,7 +89625,7 @@
         <v>466</v>
       </c>
       <c r="D1149">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E1149">
         <v>87594</v>
@@ -89748,7 +89748,7 @@
         <v>467</v>
       </c>
       <c r="D1152">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="E1152">
         <v>0</v>
@@ -89789,7 +89789,7 @@
         <v>467</v>
       </c>
       <c r="D1153">
-        <v>125.73</v>
+        <v>123.23</v>
       </c>
       <c r="E1153">
         <v>0</v>
@@ -89830,7 +89830,7 @@
         <v>466</v>
       </c>
       <c r="D1154">
-        <v>233.5</v>
+        <v>256.5</v>
       </c>
       <c r="E1154">
         <v>38930</v>
@@ -89871,7 +89871,7 @@
         <v>466</v>
       </c>
       <c r="D1155">
-        <v>1785</v>
+        <v>1755</v>
       </c>
       <c r="E1155">
         <v>5689</v>
@@ -89953,7 +89953,7 @@
         <v>467</v>
       </c>
       <c r="D1157">
-        <v>221.5</v>
+        <v>204</v>
       </c>
       <c r="E1157">
         <v>0</v>
@@ -89994,7 +89994,7 @@
         <v>467</v>
       </c>
       <c r="D1158">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E1158">
         <v>0</v>
@@ -90035,7 +90035,7 @@
         <v>466</v>
       </c>
       <c r="D1159">
-        <v>182.5</v>
+        <v>188.5</v>
       </c>
       <c r="E1159">
         <v>52974</v>
@@ -90076,7 +90076,7 @@
         <v>466</v>
       </c>
       <c r="D1160">
-        <v>86.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E1160">
         <v>105224</v>
@@ -90158,7 +90158,7 @@
         <v>467</v>
       </c>
       <c r="D1162">
-        <v>1655</v>
+        <v>1785</v>
       </c>
       <c r="E1162">
         <v>0</v>
@@ -90199,7 +90199,7 @@
         <v>466</v>
       </c>
       <c r="D1163">
-        <v>426.5</v>
+        <v>447</v>
       </c>
       <c r="E1163">
         <v>22339</v>
@@ -90322,7 +90322,7 @@
         <v>467</v>
       </c>
       <c r="D1166">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E1166">
         <v>0</v>
@@ -90363,7 +90363,7 @@
         <v>466</v>
       </c>
       <c r="D1167">
-        <v>1103.85</v>
+        <v>1039.21</v>
       </c>
       <c r="E1167">
         <v>9609</v>
@@ -90486,7 +90486,7 @@
         <v>467</v>
       </c>
       <c r="D1170">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E1170">
         <v>0</v>
@@ -90527,7 +90527,7 @@
         <v>466</v>
       </c>
       <c r="D1171">
-        <v>202.5</v>
+        <v>221.5</v>
       </c>
       <c r="E1171">
         <v>45082</v>
@@ -90650,7 +90650,7 @@
         <v>467</v>
       </c>
       <c r="D1174">
-        <v>1188.38</v>
+        <v>1113.8</v>
       </c>
       <c r="E1174">
         <v>0</v>
@@ -90691,7 +90691,7 @@
         <v>467</v>
       </c>
       <c r="D1175">
-        <v>191</v>
+        <v>190.5</v>
       </c>
       <c r="E1175">
         <v>0</v>
@@ -90732,7 +90732,7 @@
         <v>466</v>
       </c>
       <c r="D1176">
-        <v>1113.8</v>
+        <v>1173.47</v>
       </c>
       <c r="E1176">
         <v>8509</v>
@@ -90773,7 +90773,7 @@
         <v>466</v>
       </c>
       <c r="D1177">
-        <v>191</v>
+        <v>190.5</v>
       </c>
       <c r="E1177">
         <v>52418</v>
@@ -90855,7 +90855,7 @@
         <v>467</v>
       </c>
       <c r="D1179">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E1179">
         <v>0</v>
@@ -90896,7 +90896,7 @@
         <v>467</v>
       </c>
       <c r="D1180">
-        <v>1059.1</v>
+        <v>1049.16</v>
       </c>
       <c r="E1180">
         <v>0</v>
@@ -90937,7 +90937,7 @@
         <v>467</v>
       </c>
       <c r="D1181">
-        <v>176</v>
+        <v>177.5</v>
       </c>
       <c r="E1181">
         <v>0</v>
@@ -91019,7 +91019,7 @@
         <v>466</v>
       </c>
       <c r="D1183">
-        <v>1049.16</v>
+        <v>1113.8</v>
       </c>
       <c r="E1183">
         <v>8965</v>
@@ -91060,7 +91060,7 @@
         <v>466</v>
       </c>
       <c r="D1184">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E1184">
         <v>42492</v>
@@ -91142,7 +91142,7 @@
         <v>467</v>
       </c>
       <c r="D1186">
-        <v>1074.02</v>
+        <v>1148.6</v>
       </c>
       <c r="E1186">
         <v>0</v>
@@ -91224,7 +91224,7 @@
         <v>466</v>
       </c>
       <c r="D1188">
-        <v>65.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E1188">
         <v>147718</v>
@@ -91306,7 +91306,7 @@
         <v>467</v>
       </c>
       <c r="D1190">
-        <v>60.5</v>
+        <v>58.2</v>
       </c>
       <c r="E1190">
         <v>0</v>
@@ -91347,7 +91347,7 @@
         <v>467</v>
       </c>
       <c r="D1191">
-        <v>66.3</v>
+        <v>63.1</v>
       </c>
       <c r="E1191">
         <v>0</v>
@@ -91388,7 +91388,7 @@
         <v>466</v>
       </c>
       <c r="D1192">
-        <v>183</v>
+        <v>167.5</v>
       </c>
       <c r="E1192">
         <v>59616</v>
@@ -91429,7 +91429,7 @@
         <v>466</v>
       </c>
       <c r="D1193">
-        <v>388</v>
+        <v>349.5</v>
       </c>
       <c r="E1193">
         <v>28571</v>
